--- a/ig/DM-FEVRIER-2026/CodeSystem-tre-r397-categorie-entite-geographique-exercice.xlsx
+++ b/ig/DM-FEVRIER-2026/CodeSystem-tre-r397-categorie-entite-geographique-exercice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1386" uniqueCount="931">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1390" uniqueCount="935">
   <si>
     <t>Property</t>
   </si>
@@ -124,2172 +124,2175 @@
     <t>Count</t>
   </si>
   <si>
+    <t>428</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Uri</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>niveau</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#niveau</t>
+  </si>
+  <si>
+    <t>Permet d'indiquer le niveau hiérarchique du code</t>
+  </si>
+  <si>
+    <t>integer</t>
+  </si>
+  <si>
+    <t>parent</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#parent</t>
+  </si>
+  <si>
+    <t>An immediate parent of the concept in the hierarchy</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>domaine</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#domaine</t>
+  </si>
+  <si>
+    <t>Domaine de la categorie d etablissement</t>
+  </si>
+  <si>
+    <t>Coding</t>
+  </si>
+  <si>
+    <t>dateValid</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateValid</t>
+  </si>
+  <si>
+    <t>date de validité d'un code concept</t>
+  </si>
+  <si>
+    <t>dateTime</t>
+  </si>
+  <si>
+    <t>dateMaj</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateMaj</t>
+  </si>
+  <si>
+    <t>Date de mise à jour d'un code concept</t>
+  </si>
+  <si>
+    <t>dateFin</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateFin</t>
+  </si>
+  <si>
+    <t>Date de fin d'exploitation d'un code concept</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#status</t>
+  </si>
+  <si>
+    <t>A property that indicates the status of the concept.</t>
+  </si>
+  <si>
+    <t>deprecationDate</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#deprecationDate</t>
+  </si>
+  <si>
+    <t>Date Concept was deprecated</t>
+  </si>
+  <si>
+    <t>retirementDate</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#retirementDate</t>
+  </si>
+  <si>
+    <t>Date Concept was retired</t>
+  </si>
+  <si>
+    <t>specialisationRor</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#specialisationRor</t>
+  </si>
+  <si>
+    <t>Propriété permettant de spécifier les codes exclusifs appartenant au ROR</t>
+  </si>
+  <si>
+    <t>boolean</t>
+  </si>
+  <si>
+    <t>ror</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#ror</t>
+  </si>
+  <si>
+    <t>Permet de définir les codes concepts uilisés par le ROR</t>
+  </si>
+  <si>
+    <t>cisis</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#cisis</t>
+  </si>
+  <si>
+    <t>Permet de définir les codes concepts uilisés par le CISIS</t>
+  </si>
+  <si>
+    <t>rass</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#rass</t>
+  </si>
+  <si>
+    <t>Permet de définir les codes concepts uilisés par le RASS</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>Definition</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>0100</t>
+  </si>
+  <si>
+    <t>Etablissements d'administration</t>
+  </si>
+  <si>
+    <t>1000</t>
+  </si>
+  <si>
+    <t>Etablissements Relevant de la Loi Hospitalière</t>
+  </si>
+  <si>
+    <t>2000</t>
+  </si>
+  <si>
+    <t>Autres Etablissements de Soins et Prévention</t>
+  </si>
+  <si>
+    <t>3000</t>
+  </si>
+  <si>
+    <t>Autres Etablissements à Caractère Sanitaire</t>
+  </si>
+  <si>
+    <t>4000</t>
+  </si>
+  <si>
+    <t>Etab.Serv.Soc.d'Accueil Hébergement Assistance Réadaptation</t>
+  </si>
+  <si>
+    <t>5000</t>
+  </si>
+  <si>
+    <t>Etablissements et Services Sociaux d'Aide à la Famille</t>
+  </si>
+  <si>
+    <t>6000</t>
+  </si>
+  <si>
+    <t>Etab.de Formation des Personnels Sanitaires et Sociaux</t>
+  </si>
+  <si>
+    <t>0110</t>
+  </si>
+  <si>
+    <t>Etablissements d'Administration</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>1100</t>
+  </si>
+  <si>
+    <t>Etablissements Hospitaliers</t>
+  </si>
+  <si>
+    <t>1200</t>
+  </si>
+  <si>
+    <t>Autres Etablissements Relevant de la Loi Hospitalière</t>
+  </si>
+  <si>
+    <t>2100</t>
+  </si>
+  <si>
+    <t>Cabinets Libéraux</t>
+  </si>
+  <si>
+    <t>2200</t>
+  </si>
+  <si>
+    <t>3100</t>
+  </si>
+  <si>
+    <t>Laboratoires de Biologie Médicale</t>
+  </si>
+  <si>
+    <t>3200</t>
+  </si>
+  <si>
+    <t>Commerce de Biens à Usage Médicaux</t>
+  </si>
+  <si>
+    <t>3400</t>
+  </si>
+  <si>
+    <t>4100</t>
+  </si>
+  <si>
+    <t>Etab.et Serv.pour l'Enfance et la Jeunesse Handicapée</t>
+  </si>
+  <si>
+    <t>4200</t>
+  </si>
+  <si>
+    <t>Etablissements ou Classes d'Enseignement Spécial</t>
+  </si>
+  <si>
+    <t>4300</t>
+  </si>
+  <si>
+    <t>Etablissements et Services pour Adultes Handicapés</t>
+  </si>
+  <si>
+    <t>4400</t>
+  </si>
+  <si>
+    <t>Etablissements et Services pour Personnes Agées</t>
+  </si>
+  <si>
+    <t>4500</t>
+  </si>
+  <si>
+    <t>Etab.et Serv.Sociaux Concourant à la Protection de l'Enfance</t>
+  </si>
+  <si>
+    <t>4600</t>
+  </si>
+  <si>
+    <t>Autres Etab. Accueil, Hébergement, Réadaptation et Services</t>
+  </si>
+  <si>
+    <t>5100</t>
+  </si>
+  <si>
+    <t>6100</t>
+  </si>
+  <si>
+    <t>Etablissements de Formation des Personnels Sanitaires</t>
+  </si>
+  <si>
+    <t>6200</t>
+  </si>
+  <si>
+    <t>Etablissements de Formation des Personnels Sociaux</t>
+  </si>
+  <si>
+    <t>6300</t>
+  </si>
+  <si>
+    <t>Etablissements de Formation Polyvalente</t>
+  </si>
+  <si>
+    <t>0101</t>
+  </si>
+  <si>
+    <t>1101</t>
+  </si>
+  <si>
+    <t>Centres Hospitaliers Régionaux</t>
+  </si>
+  <si>
+    <t>1102</t>
+  </si>
+  <si>
+    <t>Centres Hospitaliers</t>
+  </si>
+  <si>
+    <t>1103</t>
+  </si>
+  <si>
+    <t>Centres Hospitaliers Spécialisés Lutte Maladies Mentales</t>
+  </si>
+  <si>
+    <t>1104</t>
+  </si>
+  <si>
+    <t>Centres de Lutte contre le Cancer</t>
+  </si>
+  <si>
+    <t>1106</t>
+  </si>
+  <si>
+    <t>Hôpitaux Locaux</t>
+  </si>
+  <si>
+    <t>1107</t>
+  </si>
+  <si>
+    <t>Etablissements de santé privé autorisés en SSR</t>
+  </si>
+  <si>
+    <t>1108</t>
+  </si>
+  <si>
+    <t>Centre de Moyen et de Long Séjour</t>
+  </si>
+  <si>
+    <t>1109</t>
+  </si>
+  <si>
+    <t>Etablissements de Soins de Longue Durée</t>
+  </si>
+  <si>
+    <t>1110</t>
+  </si>
+  <si>
+    <t>Etablissements de Soins de Courte Durée</t>
+  </si>
+  <si>
+    <t>1111</t>
+  </si>
+  <si>
+    <t>Autres Etablissements de Lutte contre les Maladies Mentales</t>
+  </si>
+  <si>
+    <t>1112</t>
+  </si>
+  <si>
+    <t>Etablissements d'Enfants à Caractère Sanitaire</t>
+  </si>
+  <si>
+    <t>1113</t>
+  </si>
+  <si>
+    <t>Etablissements de Lutte contre l'Alcoolisme</t>
+  </si>
+  <si>
+    <t>1201</t>
+  </si>
+  <si>
+    <t>Traitements et Soins à Domicile</t>
+  </si>
+  <si>
+    <t>1202</t>
+  </si>
+  <si>
+    <t>Santé Mentale</t>
+  </si>
+  <si>
+    <t>1203</t>
+  </si>
+  <si>
+    <t>Dialyse ambulatoire</t>
+  </si>
+  <si>
+    <t>1204</t>
+  </si>
+  <si>
+    <t>Urgence et Réanimation</t>
+  </si>
+  <si>
+    <t>1205</t>
+  </si>
+  <si>
+    <t>2101</t>
+  </si>
+  <si>
+    <t>Cabinets Libéraux de Médecins</t>
+  </si>
+  <si>
+    <t>2102</t>
+  </si>
+  <si>
+    <t>Cabinet de Groupe</t>
+  </si>
+  <si>
+    <t>2103</t>
+  </si>
+  <si>
+    <t>Autres structures d'exercice libéral</t>
+  </si>
+  <si>
+    <t>2105</t>
+  </si>
+  <si>
+    <t>Cabinet d'Auxiliaires Médicaux</t>
+  </si>
+  <si>
+    <t>2201</t>
+  </si>
+  <si>
+    <t>Dispensaires ou Centres de Soins</t>
+  </si>
+  <si>
+    <t>2202</t>
+  </si>
+  <si>
+    <t>Etablissements de PMI et de Planification Familiale</t>
+  </si>
+  <si>
+    <t>2203</t>
+  </si>
+  <si>
+    <t>Etablissements de Soins Dentaires</t>
+  </si>
+  <si>
+    <t>2204</t>
+  </si>
+  <si>
+    <t>Etablissements ne relevant pas de la Loi Hospitalière</t>
+  </si>
+  <si>
+    <t>2205</t>
+  </si>
+  <si>
+    <t>Etab.de soins relevant du service de santé des armées</t>
+  </si>
+  <si>
+    <t>2206</t>
+  </si>
+  <si>
+    <t>Centres de Santé</t>
+  </si>
+  <si>
+    <t>3101</t>
+  </si>
+  <si>
+    <t>3201</t>
+  </si>
+  <si>
+    <t>3202</t>
+  </si>
+  <si>
+    <t>Commerce de Biens Médicaux</t>
+  </si>
+  <si>
+    <t>3401</t>
+  </si>
+  <si>
+    <t>Transfusion Sanguine</t>
+  </si>
+  <si>
+    <t>3402</t>
+  </si>
+  <si>
+    <t>Conservation et Stockage d'autres Produits Humains</t>
+  </si>
+  <si>
+    <t>3403</t>
+  </si>
+  <si>
+    <t>Centre Antipoison</t>
+  </si>
+  <si>
+    <t>3404</t>
+  </si>
+  <si>
+    <t>Service d'Ambulances</t>
+  </si>
+  <si>
+    <t>3405</t>
+  </si>
+  <si>
+    <t>Installations autonomes de chirurgie esthétique</t>
+  </si>
+  <si>
+    <t>3406</t>
+  </si>
+  <si>
+    <t>Maisons de Naissance</t>
+  </si>
+  <si>
+    <t>3407</t>
+  </si>
+  <si>
+    <t>Etablissements Expérimentaux en Santé</t>
+  </si>
+  <si>
+    <t>3408</t>
+  </si>
+  <si>
+    <t>Centre de ressources transverse</t>
+  </si>
+  <si>
+    <t>3409</t>
+  </si>
+  <si>
+    <t>Services de Prévention et de Santé au Travail (SPST)</t>
+  </si>
+  <si>
+    <t>3410</t>
+  </si>
+  <si>
+    <t>Services d'incendie et de secours</t>
+  </si>
+  <si>
+    <t>4101</t>
+  </si>
+  <si>
+    <t>Etab.Educ.Spéciale pour Déficients Mentaux et Handicapés</t>
+  </si>
+  <si>
+    <t>4102</t>
+  </si>
+  <si>
+    <t>Etab.Educ Spéciale pour Enfants Trouble Conduite et Comport</t>
+  </si>
+  <si>
+    <t>4103</t>
+  </si>
+  <si>
+    <t>Etablissements d'Education Spéciale pour Handicapés Moteurs</t>
+  </si>
+  <si>
+    <t>4104</t>
+  </si>
+  <si>
+    <t>Etab.Education Spéciale pour Déficients Sensoriels</t>
+  </si>
+  <si>
+    <t>4105</t>
+  </si>
+  <si>
+    <t>Etablissements et Services Hébergement Enfants Handicapés</t>
+  </si>
+  <si>
+    <t>4106</t>
+  </si>
+  <si>
+    <t>Services à Domicile ou Ambulatoires pour Handicapés</t>
+  </si>
+  <si>
+    <t>4107</t>
+  </si>
+  <si>
+    <t>Etab. Expérimentaux en Faveur de l'Enfance Handicapée</t>
+  </si>
+  <si>
+    <t>4201</t>
+  </si>
+  <si>
+    <t>Etablissements ou Classes de Pré-Élémentaire et Élémentaire</t>
+  </si>
+  <si>
+    <t>4202</t>
+  </si>
+  <si>
+    <t>Etablissements d'Enseignement Secondaire</t>
+  </si>
+  <si>
+    <t>4301</t>
+  </si>
+  <si>
+    <t>Etab. et Services d'Hébergement pour Adultes Handicapés</t>
+  </si>
+  <si>
+    <t>4302</t>
+  </si>
+  <si>
+    <t>Etab.et Services de Travail Protégé pour Adultes Handicapés</t>
+  </si>
+  <si>
+    <t>4303</t>
+  </si>
+  <si>
+    <t>Etab.et Services de Réinsertion Prof pour Adultes Handicapés</t>
+  </si>
+  <si>
+    <t>4304</t>
+  </si>
+  <si>
+    <t>Etab.Expérimentaux en Faveur des Adultes Handicapés</t>
+  </si>
+  <si>
+    <t>4305</t>
+  </si>
+  <si>
+    <t>Services de Maintien à Domicile pour Handicapés</t>
+  </si>
+  <si>
+    <t>4401</t>
+  </si>
+  <si>
+    <t>Etablissements d'Hébergement pour Personnes Âgées</t>
+  </si>
+  <si>
+    <t>4402</t>
+  </si>
+  <si>
+    <t>Services de Maintien à Domicile pour Personnes Âgées</t>
+  </si>
+  <si>
+    <t>4403</t>
+  </si>
+  <si>
+    <t>Services Sociaux en Faveur des Personnes Âgées</t>
+  </si>
+  <si>
+    <t>4404</t>
+  </si>
+  <si>
+    <t>Etablissements Expérimentaux en Faveur des Personnes Âgées</t>
+  </si>
+  <si>
+    <t>4501</t>
+  </si>
+  <si>
+    <t>Etablissements de l'Aide Sociale à l'Enfance</t>
+  </si>
+  <si>
+    <t>4502</t>
+  </si>
+  <si>
+    <t>Etab.et Services du Ministère de la Justice pour Mineurs</t>
+  </si>
+  <si>
+    <t>4504</t>
+  </si>
+  <si>
+    <t>Services Concourant à la Protection de l'Enfance</t>
+  </si>
+  <si>
+    <t>4505</t>
+  </si>
+  <si>
+    <t>Etab. Expérimentaux en Faveur de l'Enfance Protégée</t>
+  </si>
+  <si>
+    <t>4601</t>
+  </si>
+  <si>
+    <t>Etablissements pour Adultes et Familles en Difficulté</t>
+  </si>
+  <si>
+    <t>4602</t>
+  </si>
+  <si>
+    <t>Autres Etablissements Sociaux d'Hébergement et d'Accueil</t>
+  </si>
+  <si>
+    <t>4603</t>
+  </si>
+  <si>
+    <t>Etablissements Expérimentaux en Faveur des Adultes</t>
+  </si>
+  <si>
+    <t>4604</t>
+  </si>
+  <si>
+    <t>Autres Etablissements médico-sociaux</t>
+  </si>
+  <si>
+    <t>4605</t>
+  </si>
+  <si>
+    <t>Etablissements et services multi-clientèles</t>
+  </si>
+  <si>
+    <t>4606</t>
+  </si>
+  <si>
+    <t>Centres de ressources</t>
+  </si>
+  <si>
+    <t>4607</t>
+  </si>
+  <si>
+    <t>Logements en Structure Collective</t>
+  </si>
+  <si>
+    <t>4608</t>
+  </si>
+  <si>
+    <t>Protection des majeurs</t>
+  </si>
+  <si>
+    <t>4609</t>
+  </si>
+  <si>
+    <t>Centres prestataires de services pr personnes cérébro-lésées</t>
+  </si>
+  <si>
+    <t>5101</t>
+  </si>
+  <si>
+    <t>Etablissements Garde d'Enfants d'Age pré-Scolaire</t>
+  </si>
+  <si>
+    <t>5102</t>
+  </si>
+  <si>
+    <t>Etablissements d'Hébergement pour Enfants d'Age Scolaire</t>
+  </si>
+  <si>
+    <t>5103</t>
+  </si>
+  <si>
+    <t>Etablissements Sociaux pour Loisirs et Vacances</t>
+  </si>
+  <si>
+    <t>5104</t>
+  </si>
+  <si>
+    <t>Etablissements ou Services Divers d'Aide à la Famille</t>
+  </si>
+  <si>
+    <t>6101</t>
+  </si>
+  <si>
+    <t>6102</t>
+  </si>
+  <si>
+    <t>Etablissements de Formation des Personnels Techniques</t>
+  </si>
+  <si>
+    <t>6103</t>
+  </si>
+  <si>
+    <t>Autres Etablissements de Formation des Personnels Techniques</t>
+  </si>
+  <si>
+    <t>6201</t>
+  </si>
+  <si>
+    <t>6301</t>
+  </si>
+  <si>
+    <t>001</t>
+  </si>
+  <si>
+    <t>Autres lits de m.R.</t>
+  </si>
+  <si>
+    <t>002</t>
+  </si>
+  <si>
+    <t>Autres places de l-f.</t>
+  </si>
+  <si>
+    <t>003</t>
+  </si>
+  <si>
+    <t>Autres lits de l-s</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>Centre Hospitalier Régional (C.H.R.)</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>Centre hospitalier, ex Hôpital local</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>Etablissement de Convalescence et de Repos</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>Etablissement de santé privé autorisé en SSR</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>Centre de Convalescence Cure ou Réadaptation</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>Hôpital des armées</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>Etablissement de Soins du Service de Santé des Armées</t>
+  </si>
+  <si>
+    <t>119</t>
+  </si>
+  <si>
+    <t>Maison de Régime</t>
+  </si>
+  <si>
+    <t>122</t>
+  </si>
+  <si>
+    <t>Etablissement Soins Obstétriques Chirurgico-Gynécologiques</t>
+  </si>
+  <si>
+    <t>124</t>
+  </si>
+  <si>
+    <t>Centre de Santé</t>
+  </si>
+  <si>
+    <t>125</t>
+  </si>
+  <si>
+    <t>Centre de Santé Dentaire</t>
+  </si>
+  <si>
+    <t>126</t>
+  </si>
+  <si>
+    <t>Etablissement Thermal</t>
+  </si>
+  <si>
+    <t>127</t>
+  </si>
+  <si>
+    <t>Hospitalisation à Domicile</t>
+  </si>
+  <si>
+    <t>128</t>
+  </si>
+  <si>
+    <t>Etablissement de Soins Chirurgicaux</t>
+  </si>
+  <si>
+    <t>129</t>
+  </si>
+  <si>
+    <t>Etablissement de Soins Médicaux</t>
+  </si>
+  <si>
+    <t>130</t>
+  </si>
+  <si>
+    <t>Centre de Soins Médicaux</t>
+  </si>
+  <si>
+    <t>131</t>
+  </si>
+  <si>
+    <t>Centre de Lutte Contre Cancer</t>
+  </si>
+  <si>
+    <t>132</t>
+  </si>
+  <si>
+    <t>Etablissement de Transfusion Sanguine</t>
+  </si>
+  <si>
+    <t>135</t>
+  </si>
+  <si>
+    <t>Etablissement Réadaptation Fonctionnelle</t>
+  </si>
+  <si>
+    <t>136</t>
+  </si>
+  <si>
+    <t>Banque de Sperme</t>
+  </si>
+  <si>
+    <t>137</t>
+  </si>
+  <si>
+    <t>Banque d'Organes</t>
+  </si>
+  <si>
+    <t>138</t>
+  </si>
+  <si>
+    <t>Centre de Dialyse Périodique</t>
+  </si>
+  <si>
+    <t>139</t>
+  </si>
+  <si>
+    <t>Centre de Dialyse et d'entraînement à la Dialyse</t>
+  </si>
+  <si>
+    <t>140</t>
+  </si>
+  <si>
+    <t>Centre d'Entraînement à la Dialyse</t>
+  </si>
+  <si>
+    <t>141</t>
+  </si>
+  <si>
+    <t>Centre de dialyse</t>
+  </si>
+  <si>
+    <t>142</t>
+  </si>
+  <si>
+    <t>Dispensaire Antituberculeux</t>
+  </si>
+  <si>
+    <t>143</t>
+  </si>
+  <si>
+    <t>Centre de Vaccination BCG</t>
+  </si>
+  <si>
+    <t>144</t>
+  </si>
+  <si>
+    <t>Etablissement de Lutte Contre la Tuberculose</t>
+  </si>
+  <si>
+    <t>146</t>
+  </si>
+  <si>
+    <t>Structure d'Alternative à la dialyse en centre</t>
+  </si>
+  <si>
+    <t>156</t>
+  </si>
+  <si>
+    <t>Centre Médico-Psychologique (C.M.P.)</t>
+  </si>
+  <si>
+    <t>157</t>
+  </si>
+  <si>
+    <t>Centre de Postcure</t>
+  </si>
+  <si>
+    <t>159</t>
+  </si>
+  <si>
+    <t>Centre Parental</t>
+  </si>
+  <si>
+    <t>160</t>
+  </si>
+  <si>
+    <t>Centre de Soins Spécifiques pour Toxicomanes (C.S.S.T.)</t>
+  </si>
+  <si>
+    <t>161</t>
+  </si>
+  <si>
+    <t>Maison de Santé pour Maladies Mentales</t>
+  </si>
+  <si>
+    <t>162</t>
+  </si>
+  <si>
+    <t>Centre de Cure Ambulatoire en Alcoologie (C.C.A.A.)</t>
+  </si>
+  <si>
+    <t>163</t>
+  </si>
+  <si>
+    <t>Maison d'Enfants à Caractère Sanitaire Temporaire</t>
+  </si>
+  <si>
+    <t>164</t>
+  </si>
+  <si>
+    <t>Etablissements Expérimentaux Accueil de la Petite Enfance</t>
+  </si>
+  <si>
+    <t>165</t>
+  </si>
+  <si>
+    <t>Appartement de Coordination Thérapeutique (A.C.T.)</t>
+  </si>
+  <si>
+    <t>166</t>
+  </si>
+  <si>
+    <t>Centre Parents-Enfants de moins de 3 ans</t>
+  </si>
+  <si>
+    <t>167</t>
+  </si>
+  <si>
+    <t>Crèche Collective</t>
+  </si>
+  <si>
+    <t>168</t>
+  </si>
+  <si>
+    <t>Service Accueil Familial pour la Petite Enfance</t>
+  </si>
+  <si>
+    <t>169</t>
+  </si>
+  <si>
+    <t>Crèche Multi Accueil Collectif et Familial</t>
+  </si>
+  <si>
+    <t>170</t>
+  </si>
+  <si>
+    <t>Halte Garderie</t>
+  </si>
+  <si>
+    <t>171</t>
+  </si>
+  <si>
+    <t>Garderie et Jardin d'Enfants</t>
+  </si>
+  <si>
+    <t>172</t>
+  </si>
+  <si>
+    <t>Pouponnière à Caractère Social</t>
+  </si>
+  <si>
+    <t>173</t>
+  </si>
+  <si>
+    <t>Pouponnière à Caractère Sanitaire</t>
+  </si>
+  <si>
+    <t>174</t>
+  </si>
+  <si>
+    <t>Etablissement d'Accueil Collectif Régulier et Occasionnel</t>
+  </si>
+  <si>
+    <t>175</t>
+  </si>
+  <si>
+    <t>Foyer de l'Enfance</t>
+  </si>
+  <si>
+    <t>176</t>
+  </si>
+  <si>
+    <t>Village d'Enfants</t>
+  </si>
+  <si>
+    <t>177</t>
+  </si>
+  <si>
+    <t>Maison d'Enfants à Caractère Social</t>
+  </si>
+  <si>
+    <t>178</t>
+  </si>
+  <si>
+    <t>Ctre.Accueil- Accomp.Réduc.Risq.Usag. Drogues (C.A.A.R.U.D.)</t>
+  </si>
+  <si>
+    <t>179</t>
+  </si>
+  <si>
+    <t>Maison d'Enfants à Caractère Sanitaire Permanente</t>
+  </si>
+  <si>
+    <t>180</t>
+  </si>
+  <si>
+    <t>Lits Halte Soins Santé (L.H.S.S.)</t>
+  </si>
+  <si>
+    <t>181</t>
+  </si>
+  <si>
+    <t>Maison Familiale de Vacances</t>
+  </si>
+  <si>
+    <t>182</t>
+  </si>
+  <si>
+    <t>Service d'Éducation Spéciale et de Soins à Domicile</t>
+  </si>
+  <si>
+    <t>183</t>
+  </si>
+  <si>
+    <t>Institut Médico-Educatif (I.M.E.)</t>
+  </si>
+  <si>
+    <t>184</t>
+  </si>
+  <si>
+    <t>Institut Médico-Pédagogique (I.M.P.)</t>
+  </si>
+  <si>
+    <t>185</t>
+  </si>
+  <si>
+    <t>Institut Médico-Professionnel (I.M.Pro.)</t>
+  </si>
+  <si>
+    <t>186</t>
+  </si>
+  <si>
+    <t>Institut Thérapeutique Éducatif et Pédagogique (I.T.E.P.)</t>
+  </si>
+  <si>
+    <t>188</t>
+  </si>
+  <si>
+    <t>Etablissement pour Enfants ou Adolescents Polyhandicapés</t>
+  </si>
+  <si>
+    <t>189</t>
+  </si>
+  <si>
+    <t>Centre Médico-Psycho-Pédagogique (C.M.P.P.)</t>
+  </si>
+  <si>
+    <t>190</t>
+  </si>
+  <si>
+    <t>Centre Action Médico-Sociale Précoce (C.A.M.S.P.)</t>
+  </si>
+  <si>
+    <t>191</t>
+  </si>
+  <si>
+    <t>Etablissement pour Déficients Moteurs Cérébraux</t>
+  </si>
+  <si>
+    <t>192</t>
+  </si>
+  <si>
+    <t>Institut d'éducation motrice</t>
+  </si>
+  <si>
+    <t>193</t>
+  </si>
+  <si>
+    <t>Etablissement pour Déficients Moteurs et Moteurs Cérébraux</t>
+  </si>
+  <si>
+    <t>194</t>
+  </si>
+  <si>
+    <t>Institut pour Déficients Visuels</t>
+  </si>
+  <si>
+    <t>195</t>
+  </si>
+  <si>
+    <t>Institut pour Déficients Auditifs</t>
+  </si>
+  <si>
+    <t>196</t>
+  </si>
+  <si>
+    <t>Institut d'Education Sensorielle Sourd-Aveugle</t>
+  </si>
+  <si>
+    <t>197</t>
+  </si>
+  <si>
+    <t>Centre soins accompagnement prévention addictologie (CSAPA)</t>
+  </si>
+  <si>
+    <t>198</t>
+  </si>
+  <si>
+    <t>Établissement et Service de Préorientation</t>
+  </si>
+  <si>
+    <t>199</t>
+  </si>
+  <si>
+    <t>Hospice</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>Maison de Retraite</t>
+  </si>
+  <si>
+    <t>202</t>
+  </si>
+  <si>
+    <t>Résidences autonomie</t>
+  </si>
+  <si>
+    <t>205</t>
+  </si>
+  <si>
+    <t>Foyer Club Restaurant</t>
+  </si>
+  <si>
+    <t>207</t>
+  </si>
+  <si>
+    <t>Centre de Jour pour Personnes Agées</t>
+  </si>
+  <si>
+    <t>208</t>
+  </si>
+  <si>
+    <t>Service d'Aide Ménagère à Domicile</t>
+  </si>
+  <si>
+    <t>209</t>
+  </si>
+  <si>
+    <t>Service autonomie aide et soins (SAAS)</t>
+  </si>
+  <si>
+    <t>212</t>
+  </si>
+  <si>
+    <t>Alarme Médico-Sociale</t>
+  </si>
+  <si>
+    <t>213</t>
+  </si>
+  <si>
+    <t>Lits d'Accueil Médicalisés (L.A.M.)</t>
+  </si>
+  <si>
+    <t>214</t>
+  </si>
+  <si>
+    <t>Centre Hébergement &amp; Réinsertion Sociale (C.H.R.S.)</t>
+  </si>
+  <si>
+    <t>215</t>
+  </si>
+  <si>
+    <t>Maison Relai</t>
+  </si>
+  <si>
+    <t>216</t>
+  </si>
+  <si>
+    <t>Résidence Hôtelière à Vocation Sociale (R.H.V.S)</t>
+  </si>
+  <si>
+    <t>217</t>
+  </si>
+  <si>
+    <t>Cité de Transit</t>
+  </si>
+  <si>
+    <t>218</t>
+  </si>
+  <si>
+    <t>Aire Station Nomades</t>
+  </si>
+  <si>
+    <t>219</t>
+  </si>
+  <si>
+    <t>Autre Centre d'Accueil</t>
+  </si>
+  <si>
+    <t>220</t>
+  </si>
+  <si>
+    <t>Centre Social</t>
+  </si>
+  <si>
+    <t>221</t>
+  </si>
+  <si>
+    <t>Bureau d'Aide Psychologique Universitaire (B.A.P.U.)</t>
+  </si>
+  <si>
+    <t>223</t>
+  </si>
+  <si>
+    <t>Protection Maternelle et Infantile (P.M.I.)</t>
+  </si>
+  <si>
+    <t>224</t>
+  </si>
+  <si>
+    <t>Etablissement de Consultation Pré et Post-natale</t>
+  </si>
+  <si>
+    <t>225</t>
+  </si>
+  <si>
+    <t>Consultations de Nourrissons</t>
+  </si>
+  <si>
+    <t>228</t>
+  </si>
+  <si>
+    <t>Centre de Santé Sexuelle</t>
+  </si>
+  <si>
+    <t>229</t>
+  </si>
+  <si>
+    <t>Consultation Problèmes naissance</t>
+  </si>
+  <si>
+    <t>230</t>
+  </si>
+  <si>
+    <t>Etablissement Consultation Protection Infantile</t>
+  </si>
+  <si>
+    <t>231</t>
+  </si>
+  <si>
+    <t>Espaces de vie affective, relationnelle et sexuelle (EVARS)</t>
+  </si>
+  <si>
+    <t>233</t>
+  </si>
+  <si>
+    <t>Lactarium</t>
+  </si>
+  <si>
+    <t>236</t>
+  </si>
+  <si>
+    <t>Centre Placement Familial Socio-Educatif (C.P.F.S.E.)</t>
+  </si>
+  <si>
+    <t>237</t>
+  </si>
+  <si>
+    <t>Centre de Placement Familial Spécialisé</t>
+  </si>
+  <si>
+    <t>238</t>
+  </si>
+  <si>
+    <t>Centre d'Accueil Familial Spécialisé</t>
+  </si>
+  <si>
+    <t>241</t>
+  </si>
+  <si>
+    <t>Établissement de Placement</t>
+  </si>
+  <si>
+    <t>242</t>
+  </si>
+  <si>
+    <t>Service d’Activité de Jour</t>
+  </si>
+  <si>
+    <t>246</t>
+  </si>
+  <si>
+    <t>Etablissement et Service d'Aide par le Travail (E.S.A.T.)</t>
+  </si>
+  <si>
+    <t>247</t>
+  </si>
+  <si>
+    <t>Entreprise adaptée</t>
+  </si>
+  <si>
+    <t>249</t>
+  </si>
+  <si>
+    <t>Établissement et Service de Réadaptation Professionnelle</t>
+  </si>
+  <si>
+    <t>250</t>
+  </si>
+  <si>
+    <t>Centre Réentrainement au travail</t>
+  </si>
+  <si>
+    <t>251</t>
+  </si>
+  <si>
+    <t>Maison Vacances pour Handicapés</t>
+  </si>
+  <si>
+    <t>252</t>
+  </si>
+  <si>
+    <t>Foyer Hébergement Adultes Handicapés</t>
+  </si>
+  <si>
+    <t>253</t>
+  </si>
+  <si>
+    <t>Foyer d'Accueil Polyvalent pour Adultes Handicapés</t>
+  </si>
+  <si>
+    <t>255</t>
+  </si>
+  <si>
+    <t>Maison d'Accueil Spécialisée (M.A.S.)</t>
+  </si>
+  <si>
+    <t>256</t>
+  </si>
+  <si>
+    <t>Foyer Travailleurs Migrants non transformé en Résidence Soc.</t>
+  </si>
+  <si>
+    <t>257</t>
+  </si>
+  <si>
+    <t>Foyers de jeunes travailleurs</t>
+  </si>
+  <si>
+    <t>258</t>
+  </si>
+  <si>
+    <t>Maisons Relais - Pensions de Famille</t>
+  </si>
+  <si>
+    <t>259</t>
+  </si>
+  <si>
+    <t>Autres résidences sociales</t>
+  </si>
+  <si>
+    <t>261</t>
+  </si>
+  <si>
+    <t>D.D.A.S.S.</t>
+  </si>
+  <si>
+    <t>262</t>
+  </si>
+  <si>
+    <t>Etablissement Régional d'Enseignement Adapté</t>
+  </si>
+  <si>
+    <t>265</t>
+  </si>
+  <si>
+    <t>Section Education Spéciale Classe Atelier</t>
+  </si>
+  <si>
+    <t>266</t>
+  </si>
+  <si>
+    <t>Dispensaire Antivénérien</t>
+  </si>
+  <si>
+    <t>267</t>
+  </si>
+  <si>
+    <t>Dispensaire Antihansénien</t>
+  </si>
+  <si>
+    <t>268</t>
+  </si>
+  <si>
+    <t>Centre Médico-Scolaire</t>
+  </si>
+  <si>
+    <t>269</t>
+  </si>
+  <si>
+    <t>Centre de Médecine Universitaire</t>
+  </si>
+  <si>
+    <t>270</t>
+  </si>
+  <si>
+    <t>Centre de Médecine Sportive</t>
+  </si>
+  <si>
+    <t>271</t>
+  </si>
+  <si>
+    <t>Maison d'accueil Hospitalière</t>
+  </si>
+  <si>
+    <t>272</t>
+  </si>
+  <si>
+    <t>Ecole d'ambulanciers</t>
+  </si>
+  <si>
+    <t>273</t>
+  </si>
+  <si>
+    <t>Institut de formation en soins infirmiers (I.F.S.I.)</t>
+  </si>
+  <si>
+    <t>274</t>
+  </si>
+  <si>
+    <t>Ecole de sages_femmes</t>
+  </si>
+  <si>
+    <t>275</t>
+  </si>
+  <si>
+    <t>Ecole de masseurs-kinésithérapeutes</t>
+  </si>
+  <si>
+    <t>276</t>
+  </si>
+  <si>
+    <t>Ecole de laborantins d'analyses médicales</t>
+  </si>
+  <si>
+    <t>277</t>
+  </si>
+  <si>
+    <t>Ecole de péricultrices</t>
+  </si>
+  <si>
+    <t>278</t>
+  </si>
+  <si>
+    <t>Etablissement de formation polyvalent</t>
+  </si>
+  <si>
+    <t>279</t>
+  </si>
+  <si>
+    <t>Ecole de service social</t>
+  </si>
+  <si>
+    <t>280</t>
+  </si>
+  <si>
+    <t>Ecole d'éducateurs spécialisés</t>
+  </si>
+  <si>
+    <t>281</t>
+  </si>
+  <si>
+    <t>Centre de formation d'aides soignants</t>
+  </si>
+  <si>
+    <t>282</t>
+  </si>
+  <si>
+    <t>Ecole de pédicures-podologues</t>
+  </si>
+  <si>
+    <t>283</t>
+  </si>
+  <si>
+    <t>Ecole de manipulateurs d'électro-radiologie</t>
+  </si>
+  <si>
+    <t>284</t>
+  </si>
+  <si>
+    <t>Ecole de travailleuses familiales</t>
+  </si>
+  <si>
+    <t>285</t>
+  </si>
+  <si>
+    <t>Centres de Loisirs sans Hébergement</t>
+  </si>
+  <si>
+    <t>286</t>
+  </si>
+  <si>
+    <t>Service de prévention spécialisée</t>
+  </si>
+  <si>
+    <t>289</t>
+  </si>
+  <si>
+    <t>Centre de Soins Infirmiers</t>
+  </si>
+  <si>
+    <t>292</t>
+  </si>
+  <si>
+    <t>Centre Hospitalier Spécialisé lutte Maladies Mentales</t>
+  </si>
+  <si>
+    <t>294</t>
+  </si>
+  <si>
+    <t>Centre de Consultations Cancer</t>
+  </si>
+  <si>
+    <t>295</t>
+  </si>
+  <si>
+    <t>Service AEMO et AED</t>
+  </si>
+  <si>
+    <t>297</t>
+  </si>
+  <si>
+    <t>Dispensaire Polyvalent</t>
+  </si>
+  <si>
+    <t>300</t>
+  </si>
+  <si>
+    <t>Ecoles Formant aux Professions Sanitaires</t>
+  </si>
+  <si>
+    <t>303</t>
+  </si>
+  <si>
+    <t>Ecole de conseillers en économie sociale et familiale</t>
+  </si>
+  <si>
+    <t>304</t>
+  </si>
+  <si>
+    <t>Ecole d'ergothérapeutes</t>
+  </si>
+  <si>
+    <t>305</t>
+  </si>
+  <si>
+    <t>Ecole de psycho-motriciens</t>
+  </si>
+  <si>
+    <t>306</t>
+  </si>
+  <si>
+    <t>Ecole d'infirmiers anesthésistes</t>
+  </si>
+  <si>
+    <t>307</t>
+  </si>
+  <si>
+    <t>Ecole d'infirmiers de bloc opératoire</t>
+  </si>
+  <si>
+    <t>308</t>
+  </si>
+  <si>
+    <t>Centre de formation professionnelle de secteur psychiatrique</t>
+  </si>
+  <si>
+    <t>309</t>
+  </si>
+  <si>
+    <t>Ecole de cadres infirmiers</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>Ecole de cadres de secteur psychiatrique</t>
+  </si>
+  <si>
+    <t>311</t>
+  </si>
+  <si>
+    <t>Ecole de cadres de masseurs-kinésithérapeutes</t>
+  </si>
+  <si>
+    <t>312</t>
+  </si>
+  <si>
+    <t>Ecole de cadres de manipulateurs d'électro-radiologie</t>
+  </si>
+  <si>
+    <t>313</t>
+  </si>
+  <si>
+    <t>Ecole d'éducateurs de jeunes enfants</t>
+  </si>
+  <si>
+    <t>314</t>
+  </si>
+  <si>
+    <t>Ecole d'éducateurs techniques spécialisés</t>
+  </si>
+  <si>
+    <t>315</t>
+  </si>
+  <si>
+    <t>Ecole de moniteurs-éducateurs</t>
+  </si>
+  <si>
+    <t>316</t>
+  </si>
+  <si>
+    <t>Ecole d'aides médico-psychologiques</t>
+  </si>
+  <si>
+    <t>317</t>
+  </si>
+  <si>
+    <t>Ecole d'animateurs socio-éducatifs</t>
+  </si>
+  <si>
+    <t>319</t>
+  </si>
+  <si>
+    <t>Inst. régional de formation des travailleurs sociaux</t>
+  </si>
+  <si>
+    <t>320</t>
+  </si>
+  <si>
+    <t>S.A.M.U. et Centre 15</t>
+  </si>
+  <si>
+    <t>321</t>
+  </si>
+  <si>
+    <t>Unité Mobile Hospitalière</t>
+  </si>
+  <si>
+    <t>322</t>
+  </si>
+  <si>
+    <t>Centre Rég.Informatiq.Hospit.</t>
+  </si>
+  <si>
+    <t>324</t>
+  </si>
+  <si>
+    <t>Logement Foyer non Spécialisé</t>
+  </si>
+  <si>
+    <t>326</t>
+  </si>
+  <si>
+    <t>Ecole de cadres</t>
+  </si>
+  <si>
+    <t>327</t>
+  </si>
+  <si>
+    <t>328</t>
+  </si>
+  <si>
+    <t>Centre Consultation Soins Dentaire</t>
+  </si>
+  <si>
+    <t>329</t>
+  </si>
+  <si>
+    <t>Sectorisation Psychiatrique</t>
+  </si>
+  <si>
+    <t>330</t>
+  </si>
+  <si>
+    <t>Ecoles Formant aux Professions Sociales</t>
+  </si>
+  <si>
+    <t>340</t>
+  </si>
+  <si>
+    <t>Service mandataire judiciaire à la protection des majeurs</t>
+  </si>
+  <si>
+    <t>341</t>
+  </si>
+  <si>
+    <t>Service dédié mesures d'accompagnement social personnalisé</t>
+  </si>
+  <si>
+    <t>342</t>
+  </si>
+  <si>
+    <t>Service d'information et de soutien aux tuteurs familiaux</t>
+  </si>
+  <si>
+    <t>343</t>
+  </si>
+  <si>
+    <t>Equipe Préparation et Suite Reclassement (EPSR)</t>
+  </si>
+  <si>
+    <t>344</t>
+  </si>
+  <si>
+    <t>Service délégué aux prestations familiales</t>
+  </si>
+  <si>
+    <t>345</t>
+  </si>
+  <si>
+    <t>Service Tutelle Prestation Sociale</t>
+  </si>
+  <si>
+    <t>346</t>
+  </si>
+  <si>
+    <t>Service de Travailleuses Familiales</t>
+  </si>
+  <si>
+    <t>347</t>
+  </si>
+  <si>
+    <t>Centre d'Examens de Santé</t>
+  </si>
+  <si>
+    <t>349</t>
+  </si>
+  <si>
+    <t>Ecole de cadres de sages-femmes</t>
+  </si>
+  <si>
+    <t>350</t>
+  </si>
+  <si>
+    <t>Centre de formation d'auxiliaires de puériculture</t>
+  </si>
+  <si>
+    <t>352</t>
+  </si>
+  <si>
+    <t>Centre de Psychothérapie</t>
+  </si>
+  <si>
+    <t>353</t>
+  </si>
+  <si>
+    <t>Hôpital de Jour Spécialités Médicales</t>
+  </si>
+  <si>
+    <t>354</t>
+  </si>
+  <si>
+    <t>Service de Soins Infirmiers A Domicile (S.S.I.A.D)</t>
+  </si>
+  <si>
+    <t>355</t>
+  </si>
+  <si>
+    <t>Centre Hospitalier (C.H.)</t>
+  </si>
+  <si>
+    <t>357</t>
+  </si>
+  <si>
+    <t>Association Aide aux Insuffisants Respiratoires</t>
+  </si>
+  <si>
+    <t>359</t>
+  </si>
+  <si>
+    <t>Centre Circonscription Sanitaire et Sociale</t>
+  </si>
+  <si>
+    <t>361</t>
+  </si>
+  <si>
+    <t>Centre de Cure Médicale</t>
+  </si>
+  <si>
+    <t>362</t>
+  </si>
+  <si>
+    <t>Etablissement de Soins Longue Durée</t>
+  </si>
+  <si>
+    <t>363</t>
+  </si>
+  <si>
+    <t>Centre moyen et long séjour</t>
+  </si>
+  <si>
+    <t>365</t>
+  </si>
+  <si>
+    <t>Etablissement de Soins Pluridisciplinaire</t>
+  </si>
+  <si>
+    <t>366</t>
+  </si>
+  <si>
+    <t>Atelier Thérapeutique</t>
+  </si>
+  <si>
+    <t>367</t>
+  </si>
+  <si>
+    <t>Maison d'Enfants non Conventionnée ni Habilitée</t>
+  </si>
+  <si>
+    <t>368</t>
+  </si>
+  <si>
+    <t>Service de Repas à Domicile</t>
+  </si>
+  <si>
+    <t>369</t>
+  </si>
+  <si>
+    <t>Centre Adaptation Vie Active (C.A.V.A.)</t>
+  </si>
+  <si>
+    <t>370</t>
+  </si>
+  <si>
+    <t>Etablissement Expérimental pour personnes handicapées</t>
+  </si>
+  <si>
+    <t>371</t>
+  </si>
+  <si>
+    <t>Service Action Socio-Educative pour Familles en difficulté</t>
+  </si>
+  <si>
+    <t>373</t>
+  </si>
+  <si>
+    <t>Centre de formation supérieure des travailleurs sociaux</t>
+  </si>
+  <si>
+    <t>374</t>
+  </si>
+  <si>
+    <t>Ecole Nationale Santé Publique (E.N.S.P.)</t>
+  </si>
+  <si>
+    <t>375</t>
+  </si>
+  <si>
+    <t>Classe d'Adaptation</t>
+  </si>
+  <si>
+    <t>376</t>
+  </si>
+  <si>
+    <t>Classe Spéciale Ecole Primaire</t>
+  </si>
+  <si>
+    <t>377</t>
+  </si>
+  <si>
+    <t>Etablissement Expérimental pour Enfance Handicapée</t>
+  </si>
+  <si>
+    <t>378</t>
+  </si>
+  <si>
+    <t>Etablissement Expérimental Enfance Protégée</t>
+  </si>
+  <si>
+    <t>379</t>
+  </si>
+  <si>
+    <t>Etablissement Expérimental pour Adultes Handicapés</t>
+  </si>
+  <si>
+    <t>380</t>
+  </si>
+  <si>
+    <t>Etablissement Expérimental Autres Adultes</t>
+  </si>
+  <si>
+    <t>381</t>
+  </si>
+  <si>
+    <t>Etablissement Expérimental pour Personnes Agées</t>
+  </si>
+  <si>
+    <t>382</t>
+  </si>
+  <si>
+    <t>Foyer de Vie pour Adultes Handicapés</t>
+  </si>
+  <si>
+    <t>386</t>
+  </si>
+  <si>
+    <t>Ecole Secondaire Spéciale</t>
+  </si>
+  <si>
+    <t>390</t>
+  </si>
+  <si>
+    <t>Etablissement d'Accueil Temporaire d'Enfants Handicapés</t>
+  </si>
+  <si>
+    <t>393</t>
+  </si>
+  <si>
+    <t>Autre résidence But lucratif pr personnes Âgées</t>
+  </si>
+  <si>
+    <t>394</t>
+  </si>
+  <si>
+    <t>Etablissement d'Accueil Temporaire pour Personnes Agées</t>
+  </si>
+  <si>
+    <t>395</t>
+  </si>
+  <si>
+    <t>Etablissement d'Accueil Temporaire pour Adultes Handicapés</t>
+  </si>
+  <si>
+    <t>396</t>
+  </si>
+  <si>
+    <t>Foyer Hébergement Enfants et Adolescents Handicapés</t>
+  </si>
+  <si>
+    <t>397</t>
+  </si>
+  <si>
+    <t>Service Auxiliaire de Vie pour Handicapés</t>
+  </si>
+  <si>
+    <t>398</t>
+  </si>
+  <si>
+    <t>Crèche Parentale</t>
+  </si>
+  <si>
+    <t>399</t>
+  </si>
+  <si>
+    <t>Halte Garderie Parentale</t>
+  </si>
+  <si>
+    <t>400</t>
+  </si>
+  <si>
+    <t>Centre de Services pour Associations</t>
+  </si>
+  <si>
+    <t>401</t>
+  </si>
+  <si>
+    <t>D.R.A.S.S.</t>
+  </si>
+  <si>
+    <t>402</t>
+  </si>
+  <si>
+    <t>Jardin d'Enfants Spécialisé</t>
+  </si>
+  <si>
+    <t>403</t>
+  </si>
+  <si>
+    <t>Service Social Spécialisé ou Polyvalent de Catégorie</t>
+  </si>
+  <si>
+    <t>404</t>
+  </si>
+  <si>
+    <t>Etablissement Acc.Collect.Parental Régulier &amp; Occasionnel</t>
+  </si>
+  <si>
+    <t>405</t>
+  </si>
+  <si>
+    <t>Service Social Polyvalent de Secteur</t>
+  </si>
+  <si>
+    <t>411</t>
+  </si>
+  <si>
+    <t>Intermédiaire de Placement Social</t>
+  </si>
+  <si>
+    <t>412</t>
+  </si>
+  <si>
+    <t>Appartement Thérapeutique</t>
+  </si>
+  <si>
+    <t>413</t>
+  </si>
+  <si>
+    <t>C.E.C.O.S</t>
+  </si>
+  <si>
+    <t>414</t>
+  </si>
+  <si>
+    <t>Centre Anti Poison</t>
+  </si>
+  <si>
+    <t>415</t>
+  </si>
+  <si>
+    <t>Service Médico-Psychologique Régional (S.M.P.R.)</t>
+  </si>
+  <si>
+    <t>418</t>
+  </si>
+  <si>
+    <t>Service d'Enquêtes Sociales (S.E.S.)</t>
+  </si>
+  <si>
+    <t>419</t>
+  </si>
+  <si>
+    <t>Centre d'Accueil Toxicomanes</t>
+  </si>
+  <si>
+    <t>420</t>
+  </si>
+  <si>
+    <t>Entreprise d'Insertion</t>
+  </si>
+  <si>
+    <t>421</t>
+  </si>
+  <si>
+    <t>Centre d'enseignement aux secours d'urgence</t>
+  </si>
+  <si>
+    <t>422</t>
+  </si>
+  <si>
+    <t>Traitements Spécialisés à Domicile</t>
+  </si>
+  <si>
+    <t>423</t>
+  </si>
+  <si>
+    <t>Ecole des cadres de laborantins d'analyses médicales</t>
+  </si>
+  <si>
+    <t>425</t>
+  </si>
+  <si>
+    <t>Centre d'Accueil Thérapeutique à temps partiel (C.A.T.T.P.)</t>
+  </si>
+  <si>
+    <t>426</t>
+  </si>
+  <si>
+    <t>Syndicat Inter Hospitalier (S.I.H.)</t>
+  </si>
+  <si>
     <t>427</t>
   </si>
   <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Uri</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>niveau</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#niveau</t>
-  </si>
-  <si>
-    <t>Permet d'indiquer le niveau hiérarchique du code</t>
-  </si>
-  <si>
-    <t>integer</t>
-  </si>
-  <si>
-    <t>parent</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/concept-properties#parent</t>
-  </si>
-  <si>
-    <t>An immediate parent of the concept in the hierarchy</t>
-  </si>
-  <si>
-    <t>code</t>
-  </si>
-  <si>
-    <t>domaine</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#domaine</t>
-  </si>
-  <si>
-    <t>Domaine de la categorie d etablissement</t>
-  </si>
-  <si>
-    <t>Coding</t>
-  </si>
-  <si>
-    <t>dateValid</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateValid</t>
-  </si>
-  <si>
-    <t>date de validité d'un code concept</t>
-  </si>
-  <si>
-    <t>dateTime</t>
-  </si>
-  <si>
-    <t>dateMaj</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateMaj</t>
-  </si>
-  <si>
-    <t>Date de mise à jour d'un code concept</t>
-  </si>
-  <si>
-    <t>dateFin</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateFin</t>
-  </si>
-  <si>
-    <t>Date de fin d'exploitation d'un code concept</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/concept-properties#status</t>
-  </si>
-  <si>
-    <t>A property that indicates the status of the concept.</t>
-  </si>
-  <si>
-    <t>deprecationDate</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/concept-properties#deprecationDate</t>
-  </si>
-  <si>
-    <t>Date Concept was deprecated</t>
-  </si>
-  <si>
-    <t>retirementDate</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/concept-properties#retirementDate</t>
-  </si>
-  <si>
-    <t>Date Concept was retired</t>
-  </si>
-  <si>
-    <t>specialisationRor</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#specialisationRor</t>
-  </si>
-  <si>
-    <t>Propriété permettant de spécifier les codes exclusifs appartenant au ROR</t>
-  </si>
-  <si>
-    <t>boolean</t>
-  </si>
-  <si>
-    <t>ror</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#ror</t>
-  </si>
-  <si>
-    <t>Permet de définir les codes concepts uilisés par le ROR</t>
-  </si>
-  <si>
-    <t>cisis</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#cisis</t>
-  </si>
-  <si>
-    <t>Permet de définir les codes concepts uilisés par le CISIS</t>
-  </si>
-  <si>
-    <t>rass</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#rass</t>
-  </si>
-  <si>
-    <t>Permet de définir les codes concepts uilisés par le RASS</t>
-  </si>
-  <si>
-    <t>Level</t>
-  </si>
-  <si>
-    <t>Display</t>
-  </si>
-  <si>
-    <t>Definition</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>0100</t>
-  </si>
-  <si>
-    <t>Etablissements d'administration</t>
-  </si>
-  <si>
-    <t>1000</t>
-  </si>
-  <si>
-    <t>Etablissements Relevant de la Loi Hospitalière</t>
-  </si>
-  <si>
-    <t>2000</t>
-  </si>
-  <si>
-    <t>Autres Etablissements de Soins et Prévention</t>
-  </si>
-  <si>
-    <t>3000</t>
-  </si>
-  <si>
-    <t>Autres Etablissements à Caractère Sanitaire</t>
-  </si>
-  <si>
-    <t>4000</t>
-  </si>
-  <si>
-    <t>Etab.Serv.Soc.d'Accueil Hébergement Assistance Réadaptation</t>
-  </si>
-  <si>
-    <t>5000</t>
-  </si>
-  <si>
-    <t>Etablissements et Services Sociaux d'Aide à la Famille</t>
-  </si>
-  <si>
-    <t>6000</t>
-  </si>
-  <si>
-    <t>Etab.de Formation des Personnels Sanitaires et Sociaux</t>
-  </si>
-  <si>
-    <t>0110</t>
-  </si>
-  <si>
-    <t>Etablissements d'Administration</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>1100</t>
-  </si>
-  <si>
-    <t>Etablissements Hospitaliers</t>
-  </si>
-  <si>
-    <t>1200</t>
-  </si>
-  <si>
-    <t>Autres Etablissements Relevant de la Loi Hospitalière</t>
-  </si>
-  <si>
-    <t>2100</t>
-  </si>
-  <si>
-    <t>Cabinets Libéraux</t>
-  </si>
-  <si>
-    <t>2200</t>
-  </si>
-  <si>
-    <t>3100</t>
-  </si>
-  <si>
-    <t>Laboratoires de Biologie Médicale</t>
-  </si>
-  <si>
-    <t>3200</t>
-  </si>
-  <si>
-    <t>Commerce de Biens à Usage Médicaux</t>
-  </si>
-  <si>
-    <t>3400</t>
-  </si>
-  <si>
-    <t>4100</t>
-  </si>
-  <si>
-    <t>Etab.et Serv.pour l'Enfance et la Jeunesse Handicapée</t>
-  </si>
-  <si>
-    <t>4200</t>
-  </si>
-  <si>
-    <t>Etablissements ou Classes d'Enseignement Spécial</t>
-  </si>
-  <si>
-    <t>4300</t>
-  </si>
-  <si>
-    <t>Etablissements et Services pour Adultes Handicapés</t>
-  </si>
-  <si>
-    <t>4400</t>
-  </si>
-  <si>
-    <t>Etablissements et Services pour Personnes Agées</t>
-  </si>
-  <si>
-    <t>4500</t>
-  </si>
-  <si>
-    <t>Etab.et Serv.Sociaux Concourant à la Protection de l'Enfance</t>
-  </si>
-  <si>
-    <t>4600</t>
-  </si>
-  <si>
-    <t>Autres Etab. Accueil, Hébergement, Réadaptation et Services</t>
-  </si>
-  <si>
-    <t>5100</t>
-  </si>
-  <si>
-    <t>6100</t>
-  </si>
-  <si>
-    <t>Etablissements de Formation des Personnels Sanitaires</t>
-  </si>
-  <si>
-    <t>6200</t>
-  </si>
-  <si>
-    <t>Etablissements de Formation des Personnels Sociaux</t>
-  </si>
-  <si>
-    <t>6300</t>
-  </si>
-  <si>
-    <t>Etablissements de Formation Polyvalente</t>
-  </si>
-  <si>
-    <t>0101</t>
-  </si>
-  <si>
-    <t>1101</t>
-  </si>
-  <si>
-    <t>Centres Hospitaliers Régionaux</t>
-  </si>
-  <si>
-    <t>1102</t>
-  </si>
-  <si>
-    <t>Centres Hospitaliers</t>
-  </si>
-  <si>
-    <t>1103</t>
-  </si>
-  <si>
-    <t>Centres Hospitaliers Spécialisés Lutte Maladies Mentales</t>
-  </si>
-  <si>
-    <t>1104</t>
-  </si>
-  <si>
-    <t>Centres de Lutte contre le Cancer</t>
-  </si>
-  <si>
-    <t>1106</t>
-  </si>
-  <si>
-    <t>Hôpitaux Locaux</t>
-  </si>
-  <si>
-    <t>1107</t>
-  </si>
-  <si>
-    <t>Etablissements de santé privé autorisés en SSR</t>
-  </si>
-  <si>
-    <t>1108</t>
-  </si>
-  <si>
-    <t>Centre de Moyen et de Long Séjour</t>
-  </si>
-  <si>
-    <t>1109</t>
-  </si>
-  <si>
-    <t>Etablissements de Soins de Longue Durée</t>
-  </si>
-  <si>
-    <t>1110</t>
-  </si>
-  <si>
-    <t>Etablissements de Soins de Courte Durée</t>
-  </si>
-  <si>
-    <t>1111</t>
-  </si>
-  <si>
-    <t>Autres Etablissements de Lutte contre les Maladies Mentales</t>
-  </si>
-  <si>
-    <t>1112</t>
-  </si>
-  <si>
-    <t>Etablissements d'Enfants à Caractère Sanitaire</t>
-  </si>
-  <si>
-    <t>1113</t>
-  </si>
-  <si>
-    <t>Etablissements de Lutte contre l'Alcoolisme</t>
-  </si>
-  <si>
-    <t>1201</t>
-  </si>
-  <si>
-    <t>Traitements et Soins à Domicile</t>
-  </si>
-  <si>
-    <t>1202</t>
-  </si>
-  <si>
-    <t>Santé Mentale</t>
-  </si>
-  <si>
-    <t>1203</t>
-  </si>
-  <si>
-    <t>Dialyse ambulatoire</t>
-  </si>
-  <si>
-    <t>1204</t>
-  </si>
-  <si>
-    <t>Urgence et Réanimation</t>
-  </si>
-  <si>
-    <t>1205</t>
-  </si>
-  <si>
-    <t>2101</t>
-  </si>
-  <si>
-    <t>Cabinets Libéraux de Médecins</t>
-  </si>
-  <si>
-    <t>2102</t>
-  </si>
-  <si>
-    <t>Cabinet de Groupe</t>
-  </si>
-  <si>
-    <t>2103</t>
-  </si>
-  <si>
-    <t>Autres structures d'exercice libéral</t>
-  </si>
-  <si>
-    <t>2105</t>
-  </si>
-  <si>
-    <t>Cabinet d'Auxiliaires Médicaux</t>
-  </si>
-  <si>
-    <t>2201</t>
-  </si>
-  <si>
-    <t>Dispensaires ou Centres de Soins</t>
-  </si>
-  <si>
-    <t>2202</t>
-  </si>
-  <si>
-    <t>Etablissements de PMI et de Planification Familiale</t>
-  </si>
-  <si>
-    <t>2203</t>
-  </si>
-  <si>
-    <t>Etablissements de Soins Dentaires</t>
-  </si>
-  <si>
-    <t>2204</t>
-  </si>
-  <si>
-    <t>Etablissements ne relevant pas de la Loi Hospitalière</t>
-  </si>
-  <si>
-    <t>2205</t>
-  </si>
-  <si>
-    <t>Etab.de soins relevant du service de santé des armées</t>
-  </si>
-  <si>
-    <t>2206</t>
-  </si>
-  <si>
-    <t>Centres de Santé</t>
-  </si>
-  <si>
-    <t>3101</t>
-  </si>
-  <si>
-    <t>3201</t>
-  </si>
-  <si>
-    <t>3202</t>
-  </si>
-  <si>
-    <t>Commerce de Biens Médicaux</t>
-  </si>
-  <si>
-    <t>3401</t>
-  </si>
-  <si>
-    <t>Transfusion Sanguine</t>
-  </si>
-  <si>
-    <t>3402</t>
-  </si>
-  <si>
-    <t>Conservation et Stockage d'autres Produits Humains</t>
-  </si>
-  <si>
-    <t>3403</t>
-  </si>
-  <si>
-    <t>Centre Antipoison</t>
-  </si>
-  <si>
-    <t>3404</t>
-  </si>
-  <si>
-    <t>Service d'Ambulances</t>
-  </si>
-  <si>
-    <t>3405</t>
-  </si>
-  <si>
-    <t>Installations autonomes de chirurgie esthétique</t>
-  </si>
-  <si>
-    <t>3406</t>
-  </si>
-  <si>
-    <t>Maisons de Naissance</t>
-  </si>
-  <si>
-    <t>3407</t>
-  </si>
-  <si>
-    <t>Etablissements Expérimentaux en Santé</t>
-  </si>
-  <si>
-    <t>3408</t>
-  </si>
-  <si>
-    <t>Centre de ressources transverse</t>
-  </si>
-  <si>
-    <t>3409</t>
-  </si>
-  <si>
-    <t>Services de Prévention et de Santé au Travail (SPST)</t>
-  </si>
-  <si>
-    <t>3410</t>
-  </si>
-  <si>
-    <t>Services d'incendie et de secours</t>
-  </si>
-  <si>
-    <t>4101</t>
-  </si>
-  <si>
-    <t>Etab.Educ.Spéciale pour Déficients Mentaux et Handicapés</t>
-  </si>
-  <si>
-    <t>4102</t>
-  </si>
-  <si>
-    <t>Etab.Educ Spéciale pour Enfants Trouble Conduite et Comport</t>
-  </si>
-  <si>
-    <t>4103</t>
-  </si>
-  <si>
-    <t>Etablissements d'Education Spéciale pour Handicapés Moteurs</t>
-  </si>
-  <si>
-    <t>4104</t>
-  </si>
-  <si>
-    <t>Etab.Education Spéciale pour Déficients Sensoriels</t>
-  </si>
-  <si>
-    <t>4105</t>
-  </si>
-  <si>
-    <t>Etablissements et Services Hébergement Enfants Handicapés</t>
-  </si>
-  <si>
-    <t>4106</t>
-  </si>
-  <si>
-    <t>Services à Domicile ou Ambulatoires pour Handicapés</t>
-  </si>
-  <si>
-    <t>4107</t>
-  </si>
-  <si>
-    <t>Etab. Expérimentaux en Faveur de l'Enfance Handicapée</t>
-  </si>
-  <si>
-    <t>4201</t>
-  </si>
-  <si>
-    <t>Etablissements ou Classes de Pré-Élémentaire et Élémentaire</t>
-  </si>
-  <si>
-    <t>4202</t>
-  </si>
-  <si>
-    <t>Etablissements d'Enseignement Secondaire</t>
-  </si>
-  <si>
-    <t>4301</t>
-  </si>
-  <si>
-    <t>Etab. et Services d'Hébergement pour Adultes Handicapés</t>
-  </si>
-  <si>
-    <t>4302</t>
-  </si>
-  <si>
-    <t>Etab.et Services de Travail Protégé pour Adultes Handicapés</t>
-  </si>
-  <si>
-    <t>4303</t>
-  </si>
-  <si>
-    <t>Etab.et Services de Réinsertion Prof pour Adultes Handicapés</t>
-  </si>
-  <si>
-    <t>4304</t>
-  </si>
-  <si>
-    <t>Etab.Expérimentaux en Faveur des Adultes Handicapés</t>
-  </si>
-  <si>
-    <t>4305</t>
-  </si>
-  <si>
-    <t>Services de Maintien à Domicile pour Handicapés</t>
-  </si>
-  <si>
-    <t>4401</t>
-  </si>
-  <si>
-    <t>Etablissements d'Hébergement pour Personnes Âgées</t>
-  </si>
-  <si>
-    <t>4402</t>
-  </si>
-  <si>
-    <t>Services de Maintien à Domicile pour Personnes Âgées</t>
-  </si>
-  <si>
-    <t>4403</t>
-  </si>
-  <si>
-    <t>Services Sociaux en Faveur des Personnes Âgées</t>
-  </si>
-  <si>
-    <t>4404</t>
-  </si>
-  <si>
-    <t>Etablissements Expérimentaux en Faveur des Personnes Âgées</t>
-  </si>
-  <si>
-    <t>4501</t>
-  </si>
-  <si>
-    <t>Etablissements de l'Aide Sociale à l'Enfance</t>
-  </si>
-  <si>
-    <t>4502</t>
-  </si>
-  <si>
-    <t>Etab.et Services du Ministère de la Justice pour Mineurs</t>
-  </si>
-  <si>
-    <t>4504</t>
-  </si>
-  <si>
-    <t>Services Concourant à la Protection de l'Enfance</t>
-  </si>
-  <si>
-    <t>4505</t>
-  </si>
-  <si>
-    <t>Etab. Expérimentaux en Faveur de l'Enfance Protégée</t>
-  </si>
-  <si>
-    <t>4601</t>
-  </si>
-  <si>
-    <t>Etablissements pour Adultes et Familles en Difficulté</t>
-  </si>
-  <si>
-    <t>4602</t>
-  </si>
-  <si>
-    <t>Autres Etablissements Sociaux d'Hébergement et d'Accueil</t>
-  </si>
-  <si>
-    <t>4603</t>
-  </si>
-  <si>
-    <t>Etablissements Expérimentaux en Faveur des Adultes</t>
-  </si>
-  <si>
-    <t>4604</t>
-  </si>
-  <si>
-    <t>Autres Etablissements médico-sociaux</t>
-  </si>
-  <si>
-    <t>4605</t>
-  </si>
-  <si>
-    <t>Etablissements et services multi-clientèles</t>
-  </si>
-  <si>
-    <t>4606</t>
-  </si>
-  <si>
-    <t>Centres de ressources</t>
-  </si>
-  <si>
-    <t>4607</t>
-  </si>
-  <si>
-    <t>Logements en Structure Collective</t>
-  </si>
-  <si>
-    <t>4608</t>
-  </si>
-  <si>
-    <t>Protection des majeurs</t>
-  </si>
-  <si>
-    <t>4609</t>
-  </si>
-  <si>
-    <t>Centres prestataires de services pr personnes cérébro-lésées</t>
-  </si>
-  <si>
-    <t>5101</t>
-  </si>
-  <si>
-    <t>Etablissements Garde d'Enfants d'Age pré-Scolaire</t>
-  </si>
-  <si>
-    <t>5102</t>
-  </si>
-  <si>
-    <t>Etablissements d'Hébergement pour Enfants d'Age Scolaire</t>
-  </si>
-  <si>
-    <t>5103</t>
-  </si>
-  <si>
-    <t>Etablissements Sociaux pour Loisirs et Vacances</t>
-  </si>
-  <si>
-    <t>5104</t>
-  </si>
-  <si>
-    <t>Etablissements ou Services Divers d'Aide à la Famille</t>
-  </si>
-  <si>
-    <t>6101</t>
-  </si>
-  <si>
-    <t>6102</t>
-  </si>
-  <si>
-    <t>Etablissements de Formation des Personnels Techniques</t>
-  </si>
-  <si>
-    <t>6103</t>
-  </si>
-  <si>
-    <t>Autres Etablissements de Formation des Personnels Techniques</t>
-  </si>
-  <si>
-    <t>6201</t>
-  </si>
-  <si>
-    <t>6301</t>
-  </si>
-  <si>
-    <t>001</t>
-  </si>
-  <si>
-    <t>Autres lits de m.R.</t>
-  </si>
-  <si>
-    <t>002</t>
-  </si>
-  <si>
-    <t>Autres places de l-f.</t>
-  </si>
-  <si>
-    <t>003</t>
-  </si>
-  <si>
-    <t>Autres lits de l-s</t>
-  </si>
-  <si>
-    <t>101</t>
-  </si>
-  <si>
-    <t>Centre Hospitalier Régional (C.H.R.)</t>
-  </si>
-  <si>
-    <t>106</t>
-  </si>
-  <si>
-    <t>Centre hospitalier, ex Hôpital local</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>Etablissement de Convalescence et de Repos</t>
-  </si>
-  <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>Etablissement de santé privé autorisé en SSR</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>Centre de Convalescence Cure ou Réadaptation</t>
-  </si>
-  <si>
-    <t>114</t>
-  </si>
-  <si>
-    <t>Hôpital des armées</t>
-  </si>
-  <si>
-    <t>115</t>
-  </si>
-  <si>
-    <t>Etablissement de Soins du Service de Santé des Armées</t>
-  </si>
-  <si>
-    <t>119</t>
-  </si>
-  <si>
-    <t>Maison de Régime</t>
-  </si>
-  <si>
-    <t>122</t>
-  </si>
-  <si>
-    <t>Etablissement Soins Obstétriques Chirurgico-Gynécologiques</t>
-  </si>
-  <si>
-    <t>124</t>
-  </si>
-  <si>
-    <t>Centre de Santé</t>
-  </si>
-  <si>
-    <t>125</t>
-  </si>
-  <si>
-    <t>Centre de Santé Dentaire</t>
-  </si>
-  <si>
-    <t>126</t>
-  </si>
-  <si>
-    <t>Etablissement Thermal</t>
-  </si>
-  <si>
-    <t>127</t>
-  </si>
-  <si>
-    <t>Hospitalisation à Domicile</t>
-  </si>
-  <si>
-    <t>128</t>
-  </si>
-  <si>
-    <t>Etablissement de Soins Chirurgicaux</t>
-  </si>
-  <si>
-    <t>129</t>
-  </si>
-  <si>
-    <t>Etablissement de Soins Médicaux</t>
-  </si>
-  <si>
-    <t>130</t>
-  </si>
-  <si>
-    <t>Centre de Soins Médicaux</t>
-  </si>
-  <si>
-    <t>131</t>
-  </si>
-  <si>
-    <t>Centre de Lutte Contre Cancer</t>
-  </si>
-  <si>
-    <t>132</t>
-  </si>
-  <si>
-    <t>Etablissement de Transfusion Sanguine</t>
-  </si>
-  <si>
-    <t>135</t>
-  </si>
-  <si>
-    <t>Etablissement Réadaptation Fonctionnelle</t>
-  </si>
-  <si>
-    <t>136</t>
-  </si>
-  <si>
-    <t>Banque de Sperme</t>
-  </si>
-  <si>
-    <t>137</t>
-  </si>
-  <si>
-    <t>Banque d'Organes</t>
-  </si>
-  <si>
-    <t>138</t>
-  </si>
-  <si>
-    <t>Centre de Dialyse Périodique</t>
-  </si>
-  <si>
-    <t>139</t>
-  </si>
-  <si>
-    <t>Centre de Dialyse et d'entraînement à la Dialyse</t>
-  </si>
-  <si>
-    <t>140</t>
-  </si>
-  <si>
-    <t>Centre d'Entraînement à la Dialyse</t>
-  </si>
-  <si>
-    <t>141</t>
-  </si>
-  <si>
-    <t>Centre de dialyse</t>
-  </si>
-  <si>
-    <t>142</t>
-  </si>
-  <si>
-    <t>Dispensaire Antituberculeux</t>
-  </si>
-  <si>
-    <t>143</t>
-  </si>
-  <si>
-    <t>Centre de Vaccination BCG</t>
-  </si>
-  <si>
-    <t>144</t>
-  </si>
-  <si>
-    <t>Etablissement de Lutte Contre la Tuberculose</t>
-  </si>
-  <si>
-    <t>146</t>
-  </si>
-  <si>
-    <t>Structure d'Alternative à la dialyse en centre</t>
-  </si>
-  <si>
-    <t>156</t>
-  </si>
-  <si>
-    <t>Centre Médico-Psychologique (C.M.P.)</t>
-  </si>
-  <si>
-    <t>157</t>
-  </si>
-  <si>
-    <t>Centre de Postcure</t>
-  </si>
-  <si>
-    <t>159</t>
-  </si>
-  <si>
-    <t>Centre Parental</t>
-  </si>
-  <si>
-    <t>160</t>
-  </si>
-  <si>
-    <t>Centre de Soins Spécifiques pour Toxicomanes (C.S.S.T.)</t>
-  </si>
-  <si>
-    <t>161</t>
-  </si>
-  <si>
-    <t>Maison de Santé pour Maladies Mentales</t>
-  </si>
-  <si>
-    <t>162</t>
-  </si>
-  <si>
-    <t>Centre de Cure Ambulatoire en Alcoologie (C.C.A.A.)</t>
-  </si>
-  <si>
-    <t>163</t>
-  </si>
-  <si>
-    <t>Maison d'Enfants à Caractère Sanitaire Temporaire</t>
-  </si>
-  <si>
-    <t>164</t>
-  </si>
-  <si>
-    <t>Etablissements Expérimentaux Accueil de la Petite Enfance</t>
-  </si>
-  <si>
-    <t>165</t>
-  </si>
-  <si>
-    <t>Appartement de Coordination Thérapeutique (A.C.T.)</t>
-  </si>
-  <si>
-    <t>166</t>
-  </si>
-  <si>
-    <t>Etablissement d'Accueil Mère-Enfant</t>
-  </si>
-  <si>
-    <t>167</t>
-  </si>
-  <si>
-    <t>Crèche Collective</t>
-  </si>
-  <si>
-    <t>168</t>
-  </si>
-  <si>
-    <t>Service Accueil Familial pour la Petite Enfance</t>
-  </si>
-  <si>
-    <t>169</t>
-  </si>
-  <si>
-    <t>Crèche Multi Accueil Collectif et Familial</t>
-  </si>
-  <si>
-    <t>170</t>
-  </si>
-  <si>
-    <t>Halte Garderie</t>
-  </si>
-  <si>
-    <t>171</t>
-  </si>
-  <si>
-    <t>Garderie et Jardin d'Enfants</t>
-  </si>
-  <si>
-    <t>172</t>
-  </si>
-  <si>
-    <t>Pouponnière à Caractère Social</t>
-  </si>
-  <si>
-    <t>173</t>
-  </si>
-  <si>
-    <t>Pouponnière à Caractère Sanitaire</t>
-  </si>
-  <si>
-    <t>174</t>
-  </si>
-  <si>
-    <t>Etablissement d'Accueil Collectif Régulier et Occasionnel</t>
-  </si>
-  <si>
-    <t>175</t>
-  </si>
-  <si>
-    <t>Foyer de l'Enfance</t>
-  </si>
-  <si>
-    <t>176</t>
-  </si>
-  <si>
-    <t>Village d'Enfants</t>
-  </si>
-  <si>
-    <t>177</t>
-  </si>
-  <si>
-    <t>Maison d'Enfants à Caractère Social</t>
-  </si>
-  <si>
-    <t>178</t>
-  </si>
-  <si>
-    <t>Ctre.Accueil- Accomp.Réduc.Risq.Usag. Drogues (C.A.A.R.U.D.)</t>
-  </si>
-  <si>
-    <t>179</t>
-  </si>
-  <si>
-    <t>Maison d'Enfants à Caractère Sanitaire Permanente</t>
-  </si>
-  <si>
-    <t>180</t>
-  </si>
-  <si>
-    <t>Lits Halte Soins Santé (L.H.S.S.)</t>
-  </si>
-  <si>
-    <t>181</t>
-  </si>
-  <si>
-    <t>Maison Familiale de Vacances</t>
-  </si>
-  <si>
-    <t>182</t>
-  </si>
-  <si>
-    <t>Service d'Éducation Spéciale et de Soins à Domicile</t>
-  </si>
-  <si>
-    <t>183</t>
-  </si>
-  <si>
-    <t>Institut Médico-Educatif (I.M.E.)</t>
-  </si>
-  <si>
-    <t>184</t>
-  </si>
-  <si>
-    <t>Institut Médico-Pédagogique (I.M.P.)</t>
-  </si>
-  <si>
-    <t>185</t>
-  </si>
-  <si>
-    <t>Institut Médico-Professionnel (I.M.Pro.)</t>
-  </si>
-  <si>
-    <t>186</t>
-  </si>
-  <si>
-    <t>Institut Thérapeutique Éducatif et Pédagogique (I.T.E.P.)</t>
-  </si>
-  <si>
-    <t>188</t>
-  </si>
-  <si>
-    <t>Etablissement pour Enfants ou Adolescents Polyhandicapés</t>
-  </si>
-  <si>
-    <t>189</t>
-  </si>
-  <si>
-    <t>Centre Médico-Psycho-Pédagogique (C.M.P.P.)</t>
-  </si>
-  <si>
-    <t>190</t>
-  </si>
-  <si>
-    <t>Centre Action Médico-Sociale Précoce (C.A.M.S.P.)</t>
-  </si>
-  <si>
-    <t>191</t>
-  </si>
-  <si>
-    <t>Etablissement pour Déficients Moteurs Cérébraux</t>
-  </si>
-  <si>
-    <t>192</t>
-  </si>
-  <si>
-    <t>Institut d'éducation motrice</t>
-  </si>
-  <si>
-    <t>193</t>
-  </si>
-  <si>
-    <t>Etablissement pour Déficients Moteurs et Moteurs Cérébraux</t>
-  </si>
-  <si>
-    <t>194</t>
-  </si>
-  <si>
-    <t>Institut pour Déficients Visuels</t>
-  </si>
-  <si>
-    <t>195</t>
-  </si>
-  <si>
-    <t>Institut pour Déficients Auditifs</t>
-  </si>
-  <si>
-    <t>196</t>
-  </si>
-  <si>
-    <t>Institut d'Education Sensorielle Sourd-Aveugle</t>
-  </si>
-  <si>
-    <t>197</t>
-  </si>
-  <si>
-    <t>Centre soins accompagnement prévention addictologie (CSAPA)</t>
-  </si>
-  <si>
-    <t>198</t>
-  </si>
-  <si>
-    <t>Établissement et Service de Préorientation</t>
-  </si>
-  <si>
-    <t>199</t>
-  </si>
-  <si>
-    <t>Hospice</t>
-  </si>
-  <si>
-    <t>200</t>
-  </si>
-  <si>
-    <t>Maison de Retraite</t>
-  </si>
-  <si>
-    <t>202</t>
-  </si>
-  <si>
-    <t>Résidences autonomie</t>
-  </si>
-  <si>
-    <t>205</t>
-  </si>
-  <si>
-    <t>Foyer Club Restaurant</t>
-  </si>
-  <si>
-    <t>207</t>
-  </si>
-  <si>
-    <t>Centre de Jour pour Personnes Agées</t>
-  </si>
-  <si>
-    <t>208</t>
-  </si>
-  <si>
-    <t>Service d'Aide Ménagère à Domicile</t>
-  </si>
-  <si>
-    <t>209</t>
-  </si>
-  <si>
-    <t>Service autonomie aide et soins (SAAS)</t>
-  </si>
-  <si>
-    <t>212</t>
-  </si>
-  <si>
-    <t>Alarme Médico-Sociale</t>
-  </si>
-  <si>
-    <t>213</t>
-  </si>
-  <si>
-    <t>Lits d'Accueil Médicalisés (L.A.M.)</t>
-  </si>
-  <si>
-    <t>214</t>
-  </si>
-  <si>
-    <t>Centre Hébergement &amp; Réinsertion Sociale (C.H.R.S.)</t>
-  </si>
-  <si>
-    <t>215</t>
-  </si>
-  <si>
-    <t>Maison Relai</t>
-  </si>
-  <si>
-    <t>216</t>
-  </si>
-  <si>
-    <t>Résidence Hôtelière à Vocation Sociale (R.H.V.S)</t>
-  </si>
-  <si>
-    <t>217</t>
-  </si>
-  <si>
-    <t>Cité de Transit</t>
-  </si>
-  <si>
-    <t>218</t>
-  </si>
-  <si>
-    <t>Aire Station Nomades</t>
-  </si>
-  <si>
-    <t>219</t>
-  </si>
-  <si>
-    <t>Autre Centre d'Accueil</t>
-  </si>
-  <si>
-    <t>220</t>
-  </si>
-  <si>
-    <t>Centre Social</t>
-  </si>
-  <si>
-    <t>221</t>
-  </si>
-  <si>
-    <t>Bureau d'Aide Psychologique Universitaire (B.A.P.U.)</t>
-  </si>
-  <si>
-    <t>223</t>
-  </si>
-  <si>
-    <t>Protection Maternelle et Infantile (P.M.I.)</t>
-  </si>
-  <si>
-    <t>224</t>
-  </si>
-  <si>
-    <t>Etablissement de Consultation Pré et Post-natale</t>
-  </si>
-  <si>
-    <t>225</t>
-  </si>
-  <si>
-    <t>Consultations de Nourrissons</t>
-  </si>
-  <si>
-    <t>228</t>
-  </si>
-  <si>
-    <t>Centre de Santé Sexuelle</t>
-  </si>
-  <si>
-    <t>229</t>
-  </si>
-  <si>
-    <t>Consultation Problèmes naissance</t>
-  </si>
-  <si>
-    <t>230</t>
-  </si>
-  <si>
-    <t>Etablissement Consultation Protection Infantile</t>
-  </si>
-  <si>
-    <t>231</t>
-  </si>
-  <si>
-    <t>Espaces de vie affective, relationnelle et sexuelle (EVARS)</t>
-  </si>
-  <si>
-    <t>233</t>
-  </si>
-  <si>
-    <t>Lactarium</t>
-  </si>
-  <si>
-    <t>236</t>
-  </si>
-  <si>
-    <t>Centre Placement Familial Socio-Educatif (C.P.F.S.E.)</t>
-  </si>
-  <si>
-    <t>237</t>
-  </si>
-  <si>
-    <t>Centre de Placement Familial Spécialisé</t>
-  </si>
-  <si>
-    <t>238</t>
-  </si>
-  <si>
-    <t>Centre d'Accueil Familial Spécialisé</t>
-  </si>
-  <si>
-    <t>241</t>
-  </si>
-  <si>
-    <t>Établissement de Placement</t>
-  </si>
-  <si>
-    <t>242</t>
-  </si>
-  <si>
-    <t>Service d’Activité de Jour</t>
-  </si>
-  <si>
-    <t>246</t>
-  </si>
-  <si>
-    <t>Etablissement et Service d'Aide par le Travail (E.S.A.T.)</t>
-  </si>
-  <si>
-    <t>247</t>
-  </si>
-  <si>
-    <t>Entreprise adaptée</t>
-  </si>
-  <si>
-    <t>249</t>
-  </si>
-  <si>
-    <t>Établissement et Service de Réadaptation Professionnelle</t>
-  </si>
-  <si>
-    <t>250</t>
-  </si>
-  <si>
-    <t>Centre Réentrainement au travail</t>
-  </si>
-  <si>
-    <t>251</t>
-  </si>
-  <si>
-    <t>Maison Vacances pour Handicapés</t>
-  </si>
-  <si>
-    <t>252</t>
-  </si>
-  <si>
-    <t>Foyer Hébergement Adultes Handicapés</t>
-  </si>
-  <si>
-    <t>253</t>
-  </si>
-  <si>
-    <t>Foyer d'Accueil Polyvalent pour Adultes Handicapés</t>
-  </si>
-  <si>
-    <t>255</t>
-  </si>
-  <si>
-    <t>Maison d'Accueil Spécialisée (M.A.S.)</t>
-  </si>
-  <si>
-    <t>256</t>
-  </si>
-  <si>
-    <t>Foyer Travailleurs Migrants non transformé en Résidence Soc.</t>
-  </si>
-  <si>
-    <t>257</t>
-  </si>
-  <si>
-    <t>Foyers de jeunes travailleurs</t>
-  </si>
-  <si>
-    <t>258</t>
-  </si>
-  <si>
-    <t>Maisons Relais - Pensions de Famille</t>
-  </si>
-  <si>
-    <t>259</t>
-  </si>
-  <si>
-    <t>Autres résidences sociales</t>
-  </si>
-  <si>
-    <t>261</t>
-  </si>
-  <si>
-    <t>D.D.A.S.S.</t>
-  </si>
-  <si>
-    <t>262</t>
-  </si>
-  <si>
-    <t>Etablissement Régional d'Enseignement Adapté</t>
-  </si>
-  <si>
-    <t>265</t>
-  </si>
-  <si>
-    <t>Section Education Spéciale Classe Atelier</t>
-  </si>
-  <si>
-    <t>266</t>
-  </si>
-  <si>
-    <t>Dispensaire Antivénérien</t>
-  </si>
-  <si>
-    <t>267</t>
-  </si>
-  <si>
-    <t>Dispensaire Antihansénien</t>
-  </si>
-  <si>
-    <t>268</t>
-  </si>
-  <si>
-    <t>Centre Médico-Scolaire</t>
-  </si>
-  <si>
-    <t>269</t>
-  </si>
-  <si>
-    <t>Centre de Médecine Universitaire</t>
-  </si>
-  <si>
-    <t>270</t>
-  </si>
-  <si>
-    <t>Centre de Médecine Sportive</t>
-  </si>
-  <si>
-    <t>271</t>
-  </si>
-  <si>
-    <t>Maison d'accueil Hospitalière</t>
-  </si>
-  <si>
-    <t>272</t>
-  </si>
-  <si>
-    <t>Ecole d'ambulanciers</t>
-  </si>
-  <si>
-    <t>273</t>
-  </si>
-  <si>
-    <t>Institut de formation en soins infirmiers (I.F.S.I.)</t>
-  </si>
-  <si>
-    <t>274</t>
-  </si>
-  <si>
-    <t>Ecole de sages_femmes</t>
-  </si>
-  <si>
-    <t>275</t>
-  </si>
-  <si>
-    <t>Ecole de masseurs-kinésithérapeutes</t>
-  </si>
-  <si>
-    <t>276</t>
-  </si>
-  <si>
-    <t>Ecole de laborantins d'analyses médicales</t>
-  </si>
-  <si>
-    <t>277</t>
-  </si>
-  <si>
-    <t>Ecole de péricultrices</t>
-  </si>
-  <si>
-    <t>278</t>
-  </si>
-  <si>
-    <t>Etablissement de formation polyvalent</t>
-  </si>
-  <si>
-    <t>279</t>
-  </si>
-  <si>
-    <t>Ecole de service social</t>
-  </si>
-  <si>
-    <t>280</t>
-  </si>
-  <si>
-    <t>Ecole d'éducateurs spécialisés</t>
-  </si>
-  <si>
-    <t>281</t>
-  </si>
-  <si>
-    <t>Centre de formation d'aides soignants</t>
-  </si>
-  <si>
-    <t>282</t>
-  </si>
-  <si>
-    <t>Ecole de pédicures-podologues</t>
-  </si>
-  <si>
-    <t>283</t>
-  </si>
-  <si>
-    <t>Ecole de manipulateurs d'électro-radiologie</t>
-  </si>
-  <si>
-    <t>284</t>
-  </si>
-  <si>
-    <t>Ecole de travailleuses familiales</t>
-  </si>
-  <si>
-    <t>285</t>
-  </si>
-  <si>
-    <t>Centres de Loisirs sans Hébergement</t>
-  </si>
-  <si>
-    <t>286</t>
-  </si>
-  <si>
-    <t>Club Equipe de Prévention</t>
-  </si>
-  <si>
-    <t>289</t>
-  </si>
-  <si>
-    <t>Centre de Soins Infirmiers</t>
-  </si>
-  <si>
-    <t>292</t>
-  </si>
-  <si>
-    <t>Centre Hospitalier Spécialisé lutte Maladies Mentales</t>
-  </si>
-  <si>
-    <t>294</t>
-  </si>
-  <si>
-    <t>Centre de Consultations Cancer</t>
-  </si>
-  <si>
-    <t>295</t>
-  </si>
-  <si>
-    <t>Service AEMO et AED</t>
-  </si>
-  <si>
-    <t>297</t>
-  </si>
-  <si>
-    <t>Dispensaire Polyvalent</t>
-  </si>
-  <si>
-    <t>300</t>
-  </si>
-  <si>
-    <t>Ecoles Formant aux Professions Sanitaires</t>
-  </si>
-  <si>
-    <t>303</t>
-  </si>
-  <si>
-    <t>Ecole de conseillers en économie sociale et familiale</t>
-  </si>
-  <si>
-    <t>304</t>
-  </si>
-  <si>
-    <t>Ecole d'ergothérapeutes</t>
-  </si>
-  <si>
-    <t>305</t>
-  </si>
-  <si>
-    <t>Ecole de psycho-motriciens</t>
-  </si>
-  <si>
-    <t>306</t>
-  </si>
-  <si>
-    <t>Ecole d'infirmiers anesthésistes</t>
-  </si>
-  <si>
-    <t>307</t>
-  </si>
-  <si>
-    <t>Ecole d'infirmiers de bloc opératoire</t>
-  </si>
-  <si>
-    <t>308</t>
-  </si>
-  <si>
-    <t>Centre de formation professionnelle de secteur psychiatrique</t>
-  </si>
-  <si>
-    <t>309</t>
-  </si>
-  <si>
-    <t>Ecole de cadres infirmiers</t>
-  </si>
-  <si>
-    <t>310</t>
-  </si>
-  <si>
-    <t>Ecole de cadres de secteur psychiatrique</t>
-  </si>
-  <si>
-    <t>311</t>
-  </si>
-  <si>
-    <t>Ecole de cadres de masseurs-kinésithérapeutes</t>
-  </si>
-  <si>
-    <t>312</t>
-  </si>
-  <si>
-    <t>Ecole de cadres de manipulateurs d'électro-radiologie</t>
-  </si>
-  <si>
-    <t>313</t>
-  </si>
-  <si>
-    <t>Ecole d'éducateurs de jeunes enfants</t>
-  </si>
-  <si>
-    <t>314</t>
-  </si>
-  <si>
-    <t>Ecole d'éducateurs techniques spécialisés</t>
-  </si>
-  <si>
-    <t>315</t>
-  </si>
-  <si>
-    <t>Ecole de moniteurs-éducateurs</t>
-  </si>
-  <si>
-    <t>316</t>
-  </si>
-  <si>
-    <t>Ecole d'aides médico-psychologiques</t>
-  </si>
-  <si>
-    <t>317</t>
-  </si>
-  <si>
-    <t>Ecole d'animateurs socio-éducatifs</t>
-  </si>
-  <si>
-    <t>319</t>
-  </si>
-  <si>
-    <t>Inst. régional de formation des travailleurs sociaux</t>
-  </si>
-  <si>
-    <t>320</t>
-  </si>
-  <si>
-    <t>S.A.M.U. et Centre 15</t>
-  </si>
-  <si>
-    <t>321</t>
-  </si>
-  <si>
-    <t>Unité Mobile Hospitalière</t>
-  </si>
-  <si>
-    <t>322</t>
-  </si>
-  <si>
-    <t>Centre Rég.Informatiq.Hospit.</t>
-  </si>
-  <si>
-    <t>324</t>
-  </si>
-  <si>
-    <t>Logement Foyer non Spécialisé</t>
-  </si>
-  <si>
-    <t>326</t>
-  </si>
-  <si>
-    <t>Ecole de cadres</t>
-  </si>
-  <si>
-    <t>327</t>
-  </si>
-  <si>
-    <t>328</t>
-  </si>
-  <si>
-    <t>Centre Consultation Soins Dentaire</t>
-  </si>
-  <si>
-    <t>329</t>
-  </si>
-  <si>
-    <t>Sectorisation Psychiatrique</t>
-  </si>
-  <si>
-    <t>330</t>
-  </si>
-  <si>
-    <t>Ecoles Formant aux Professions Sociales</t>
-  </si>
-  <si>
-    <t>340</t>
-  </si>
-  <si>
-    <t>Service mandataire judiciaire à la protection des majeurs</t>
-  </si>
-  <si>
-    <t>341</t>
-  </si>
-  <si>
-    <t>Service dédié mesures d'accompagnement social personnalisé</t>
-  </si>
-  <si>
-    <t>342</t>
-  </si>
-  <si>
-    <t>Service d'information et de soutien aux tuteurs familiaux</t>
-  </si>
-  <si>
-    <t>343</t>
-  </si>
-  <si>
-    <t>Equipe Préparation et Suite Reclassement (EPSR)</t>
-  </si>
-  <si>
-    <t>344</t>
-  </si>
-  <si>
-    <t>Service délégué aux prestations familiales</t>
-  </si>
-  <si>
-    <t>345</t>
-  </si>
-  <si>
-    <t>Service Tutelle Prestation Sociale</t>
-  </si>
-  <si>
-    <t>346</t>
-  </si>
-  <si>
-    <t>Service de Travailleuses Familiales</t>
-  </si>
-  <si>
-    <t>347</t>
-  </si>
-  <si>
-    <t>Centre d'Examens de Santé</t>
-  </si>
-  <si>
-    <t>349</t>
-  </si>
-  <si>
-    <t>Ecole de cadres de sages-femmes</t>
-  </si>
-  <si>
-    <t>350</t>
-  </si>
-  <si>
-    <t>Centre de formation d'auxiliaires de puériculture</t>
-  </si>
-  <si>
-    <t>352</t>
-  </si>
-  <si>
-    <t>Centre de Psychothérapie</t>
-  </si>
-  <si>
-    <t>353</t>
-  </si>
-  <si>
-    <t>Hôpital de Jour Spécialités Médicales</t>
-  </si>
-  <si>
-    <t>354</t>
-  </si>
-  <si>
-    <t>Service de Soins Infirmiers A Domicile (S.S.I.A.D)</t>
-  </si>
-  <si>
-    <t>355</t>
-  </si>
-  <si>
-    <t>Centre Hospitalier (C.H.)</t>
-  </si>
-  <si>
-    <t>357</t>
-  </si>
-  <si>
-    <t>Association Aide aux Insuffisants Respiratoires</t>
-  </si>
-  <si>
-    <t>359</t>
-  </si>
-  <si>
-    <t>Centre Circonscription Sanitaire et Sociale</t>
-  </si>
-  <si>
-    <t>361</t>
-  </si>
-  <si>
-    <t>Centre de Cure Médicale</t>
-  </si>
-  <si>
-    <t>362</t>
-  </si>
-  <si>
-    <t>Etablissement de Soins Longue Durée</t>
-  </si>
-  <si>
-    <t>363</t>
-  </si>
-  <si>
-    <t>Centre moyen et long séjour</t>
-  </si>
-  <si>
-    <t>365</t>
-  </si>
-  <si>
-    <t>Etablissement de Soins Pluridisciplinaire</t>
-  </si>
-  <si>
-    <t>366</t>
-  </si>
-  <si>
-    <t>Atelier Thérapeutique</t>
-  </si>
-  <si>
-    <t>367</t>
-  </si>
-  <si>
-    <t>Maison d'Enfants non Conventionnée ni Habilitée</t>
-  </si>
-  <si>
-    <t>368</t>
-  </si>
-  <si>
-    <t>Service de Repas à Domicile</t>
-  </si>
-  <si>
-    <t>369</t>
-  </si>
-  <si>
-    <t>Centre Adaptation Vie Active (C.A.V.A.)</t>
-  </si>
-  <si>
-    <t>370</t>
-  </si>
-  <si>
-    <t>Etablissement Expérimental pour personnes handicapées</t>
-  </si>
-  <si>
-    <t>371</t>
-  </si>
-  <si>
-    <t>Service Action Socio-Educative pour Familles en difficulté</t>
-  </si>
-  <si>
-    <t>373</t>
-  </si>
-  <si>
-    <t>Centre de formation supérieure des travailleurs sociaux</t>
-  </si>
-  <si>
-    <t>374</t>
-  </si>
-  <si>
-    <t>Ecole Nationale Santé Publique (E.N.S.P.)</t>
-  </si>
-  <si>
-    <t>375</t>
-  </si>
-  <si>
-    <t>Classe d'Adaptation</t>
-  </si>
-  <si>
-    <t>376</t>
-  </si>
-  <si>
-    <t>Classe Spéciale Ecole Primaire</t>
-  </si>
-  <si>
-    <t>377</t>
-  </si>
-  <si>
-    <t>Etablissement Expérimental pour Enfance Handicapée</t>
-  </si>
-  <si>
-    <t>378</t>
-  </si>
-  <si>
-    <t>Etablissement Expérimental Enfance Protégée</t>
-  </si>
-  <si>
-    <t>379</t>
-  </si>
-  <si>
-    <t>Etablissement Expérimental pour Adultes Handicapés</t>
-  </si>
-  <si>
-    <t>380</t>
-  </si>
-  <si>
-    <t>Etablissement Expérimental Autres Adultes</t>
-  </si>
-  <si>
-    <t>381</t>
-  </si>
-  <si>
-    <t>Etablissement Expérimental pour Personnes Agées</t>
-  </si>
-  <si>
-    <t>382</t>
-  </si>
-  <si>
-    <t>Foyer de Vie pour Adultes Handicapés</t>
-  </si>
-  <si>
-    <t>386</t>
-  </si>
-  <si>
-    <t>Ecole Secondaire Spéciale</t>
-  </si>
-  <si>
-    <t>390</t>
-  </si>
-  <si>
-    <t>Etablissement d'Accueil Temporaire d'Enfants Handicapés</t>
-  </si>
-  <si>
-    <t>393</t>
-  </si>
-  <si>
-    <t>Autre résidence But lucratif pr personnes Âgées</t>
-  </si>
-  <si>
-    <t>394</t>
-  </si>
-  <si>
-    <t>Etablissement d'Accueil Temporaire pour Personnes Agées</t>
-  </si>
-  <si>
-    <t>395</t>
-  </si>
-  <si>
-    <t>Etablissement d'Accueil Temporaire pour Adultes Handicapés</t>
-  </si>
-  <si>
-    <t>396</t>
-  </si>
-  <si>
-    <t>Foyer Hébergement Enfants et Adolescents Handicapés</t>
-  </si>
-  <si>
-    <t>397</t>
-  </si>
-  <si>
-    <t>Service Auxiliaire de Vie pour Handicapés</t>
-  </si>
-  <si>
-    <t>398</t>
-  </si>
-  <si>
-    <t>Crèche Parentale</t>
-  </si>
-  <si>
-    <t>399</t>
-  </si>
-  <si>
-    <t>Halte Garderie Parentale</t>
-  </si>
-  <si>
-    <t>400</t>
-  </si>
-  <si>
-    <t>Centre de Services pour Associations</t>
-  </si>
-  <si>
-    <t>401</t>
-  </si>
-  <si>
-    <t>D.R.A.S.S.</t>
-  </si>
-  <si>
-    <t>402</t>
-  </si>
-  <si>
-    <t>Jardin d'Enfants Spécialisé</t>
-  </si>
-  <si>
-    <t>403</t>
-  </si>
-  <si>
-    <t>Service Social Spécialisé ou Polyvalent de Catégorie</t>
-  </si>
-  <si>
-    <t>404</t>
-  </si>
-  <si>
-    <t>Etablissement Acc.Collect.Parental Régulier &amp; Occasionnel</t>
-  </si>
-  <si>
-    <t>405</t>
-  </si>
-  <si>
-    <t>Service Social Polyvalent de Secteur</t>
-  </si>
-  <si>
-    <t>411</t>
-  </si>
-  <si>
-    <t>Intermédiaire de Placement Social</t>
-  </si>
-  <si>
-    <t>412</t>
-  </si>
-  <si>
-    <t>Appartement Thérapeutique</t>
-  </si>
-  <si>
-    <t>413</t>
-  </si>
-  <si>
-    <t>C.E.C.O.S</t>
-  </si>
-  <si>
-    <t>414</t>
-  </si>
-  <si>
-    <t>Centre Anti Poison</t>
-  </si>
-  <si>
-    <t>415</t>
-  </si>
-  <si>
-    <t>Service Médico-Psychologique Régional (S.M.P.R.)</t>
-  </si>
-  <si>
-    <t>418</t>
-  </si>
-  <si>
-    <t>Service d'Enquêtes Sociales (S.E.S.)</t>
-  </si>
-  <si>
-    <t>419</t>
-  </si>
-  <si>
-    <t>Centre d'Accueil Toxicomanes</t>
-  </si>
-  <si>
-    <t>420</t>
-  </si>
-  <si>
-    <t>Entreprise d'Insertion</t>
-  </si>
-  <si>
-    <t>421</t>
-  </si>
-  <si>
-    <t>Centre d'enseignement aux secours d'urgence</t>
-  </si>
-  <si>
-    <t>422</t>
-  </si>
-  <si>
-    <t>Traitements Spécialisés à Domicile</t>
-  </si>
-  <si>
-    <t>423</t>
-  </si>
-  <si>
-    <t>Ecole des cadres de laborantins d'analyses médicales</t>
-  </si>
-  <si>
-    <t>425</t>
-  </si>
-  <si>
-    <t>Centre d'Accueil Thérapeutique à temps partiel (C.A.T.T.P.)</t>
-  </si>
-  <si>
-    <t>426</t>
-  </si>
-  <si>
-    <t>Syndicat Inter Hospitalier (S.I.H.)</t>
-  </si>
-  <si>
     <t>Service Educatif Auprès des Tribunaux (S.E.A.T.)</t>
   </si>
   <si>
@@ -2735,6 +2738,15 @@
   </si>
   <si>
     <t>Les centres de santé et de médiation en santé sexuelle (CSMSS) sont des établissements de santé dérogatoires relevant de l’article L. 6323-1 du code de la santé publique (CSP). Ils ont initialement fait l’objet d’une expérimentation dans le cadre du dispositif prévu à l’article 51 de la loi de financement de la sécurité sociale, au cours de laquelle ils étaient rattachés au numéro FINESS des centres de santé de droit commun. L’activité des centres de santé et de médiation en santé sexuelle (CSMSS) consiste à assurer l’accueil, l’information, la prévention, le dépistage et l’accompagnement des publics dans le domaine de la santé sexuelle dans une approche globale intégrant notamment la prévention et la prise en charge des infections sexuellement transmissibles (IST) et du VIH, la prescription de la contraception et la mise en place de parcours en santé sexuelle.</t>
+  </si>
+  <si>
+    <t>650</t>
+  </si>
+  <si>
+    <t>Dispositifs Spécifiques Régionaux en périnatalité</t>
+  </si>
+  <si>
+    <t>Les DSRP ont pour mission principale l’animation régionale des professionnels de la périnatalité et l’accompagnement des évolutions de l’offre et des pratiques, dans un contexte marqué par des enjeux forts en matière de qualité des soins, de prévention, de démographie médicale et d’organisation des parcours. Ils contribuent à la lisibilité et à la cohérence de l’offre de soins périnatals sur les territoires, en favorisant la coordination entre la ville, l’hôpital et les services de protection maternelle et infantile (PMI).</t>
   </si>
   <si>
     <t>690</t>
@@ -3324,7 +3336,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D428"/>
+  <dimension ref="A1:D429"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -7438,10 +7450,10 @@
         <v>87</v>
       </c>
       <c r="B343" t="s" s="2">
-        <v>36</v>
+        <v>758</v>
       </c>
       <c r="C343" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="D343" s="2"/>
     </row>
@@ -7450,10 +7462,10 @@
         <v>87</v>
       </c>
       <c r="B344" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="C344" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="D344" s="2"/>
     </row>
@@ -7462,10 +7474,10 @@
         <v>87</v>
       </c>
       <c r="B345" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C345" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="D345" s="2"/>
     </row>
@@ -7474,10 +7486,10 @@
         <v>87</v>
       </c>
       <c r="B346" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C346" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D346" s="2"/>
     </row>
@@ -7486,10 +7498,10 @@
         <v>87</v>
       </c>
       <c r="B347" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C347" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="D347" s="2"/>
     </row>
@@ -7498,10 +7510,10 @@
         <v>87</v>
       </c>
       <c r="B348" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C348" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="D348" s="2"/>
     </row>
@@ -7510,10 +7522,10 @@
         <v>87</v>
       </c>
       <c r="B349" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="C349" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="D349" s="2"/>
     </row>
@@ -7522,10 +7534,10 @@
         <v>87</v>
       </c>
       <c r="B350" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C350" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="D350" s="2"/>
     </row>
@@ -7534,10 +7546,10 @@
         <v>87</v>
       </c>
       <c r="B351" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C351" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="D351" s="2"/>
     </row>
@@ -7546,10 +7558,10 @@
         <v>87</v>
       </c>
       <c r="B352" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="C352" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="D352" s="2"/>
     </row>
@@ -7558,10 +7570,10 @@
         <v>87</v>
       </c>
       <c r="B353" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C353" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="D353" s="2"/>
     </row>
@@ -7570,10 +7582,10 @@
         <v>87</v>
       </c>
       <c r="B354" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C354" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="D354" s="2"/>
     </row>
@@ -7582,10 +7594,10 @@
         <v>87</v>
       </c>
       <c r="B355" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C355" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="D355" s="2"/>
     </row>
@@ -7594,10 +7606,10 @@
         <v>87</v>
       </c>
       <c r="B356" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="C356" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="D356" s="2"/>
     </row>
@@ -7606,10 +7618,10 @@
         <v>87</v>
       </c>
       <c r="B357" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C357" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="D357" s="2"/>
     </row>
@@ -7618,10 +7630,10 @@
         <v>87</v>
       </c>
       <c r="B358" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C358" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="D358" s="2"/>
     </row>
@@ -7630,10 +7642,10 @@
         <v>87</v>
       </c>
       <c r="B359" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C359" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="D359" s="2"/>
     </row>
@@ -7642,10 +7654,10 @@
         <v>87</v>
       </c>
       <c r="B360" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="C360" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="D360" s="2"/>
     </row>
@@ -7654,10 +7666,10 @@
         <v>87</v>
       </c>
       <c r="B361" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C361" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="D361" s="2"/>
     </row>
@@ -7666,10 +7678,10 @@
         <v>87</v>
       </c>
       <c r="B362" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C362" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="D362" s="2"/>
     </row>
@@ -7678,10 +7690,10 @@
         <v>87</v>
       </c>
       <c r="B363" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C363" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="D363" s="2"/>
     </row>
@@ -7690,10 +7702,10 @@
         <v>87</v>
       </c>
       <c r="B364" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="C364" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="D364" s="2"/>
     </row>
@@ -7702,10 +7714,10 @@
         <v>87</v>
       </c>
       <c r="B365" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="C365" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="D365" s="2"/>
     </row>
@@ -7714,10 +7726,10 @@
         <v>87</v>
       </c>
       <c r="B366" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="C366" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="D366" s="2"/>
     </row>
@@ -7726,10 +7738,10 @@
         <v>87</v>
       </c>
       <c r="B367" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="C367" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="D367" s="2"/>
     </row>
@@ -7738,10 +7750,10 @@
         <v>87</v>
       </c>
       <c r="B368" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="C368" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="D368" s="2"/>
     </row>
@@ -7750,10 +7762,10 @@
         <v>87</v>
       </c>
       <c r="B369" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C369" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="D369" s="2"/>
     </row>
@@ -7762,10 +7774,10 @@
         <v>87</v>
       </c>
       <c r="B370" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="C370" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="D370" s="2"/>
     </row>
@@ -7774,10 +7786,10 @@
         <v>87</v>
       </c>
       <c r="B371" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="C371" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="D371" s="2"/>
     </row>
@@ -7786,10 +7798,10 @@
         <v>87</v>
       </c>
       <c r="B372" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="C372" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D372" s="2"/>
     </row>
@@ -7798,10 +7810,10 @@
         <v>87</v>
       </c>
       <c r="B373" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="C373" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="D373" s="2"/>
     </row>
@@ -7810,10 +7822,10 @@
         <v>87</v>
       </c>
       <c r="B374" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C374" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="D374" s="2"/>
     </row>
@@ -7822,10 +7834,10 @@
         <v>87</v>
       </c>
       <c r="B375" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C375" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D375" s="2"/>
     </row>
@@ -7834,10 +7846,10 @@
         <v>87</v>
       </c>
       <c r="B376" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="C376" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="D376" s="2"/>
     </row>
@@ -7846,7 +7858,7 @@
         <v>87</v>
       </c>
       <c r="B377" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="C377" t="s" s="2">
         <v>173</v>
@@ -7858,10 +7870,10 @@
         <v>87</v>
       </c>
       <c r="B378" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C378" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="D378" s="2"/>
     </row>
@@ -7870,13 +7882,13 @@
         <v>87</v>
       </c>
       <c r="B379" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="C379" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="D379" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
     </row>
     <row r="380">
@@ -7884,7 +7896,7 @@
         <v>87</v>
       </c>
       <c r="B380" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="C380" t="s" s="2">
         <v>177</v>
@@ -7896,10 +7908,10 @@
         <v>87</v>
       </c>
       <c r="B381" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="C381" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="D381" s="2"/>
     </row>
@@ -7908,10 +7920,10 @@
         <v>87</v>
       </c>
       <c r="B382" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="C382" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="D382" s="2"/>
     </row>
@@ -7920,10 +7932,10 @@
         <v>87</v>
       </c>
       <c r="B383" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="C383" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="D383" s="2"/>
     </row>
@@ -7932,10 +7944,10 @@
         <v>87</v>
       </c>
       <c r="B384" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="C384" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="D384" s="2"/>
     </row>
@@ -7944,10 +7956,10 @@
         <v>87</v>
       </c>
       <c r="B385" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="C385" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="D385" s="2"/>
     </row>
@@ -7956,10 +7968,10 @@
         <v>87</v>
       </c>
       <c r="B386" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="C386" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="D386" s="2"/>
     </row>
@@ -7968,10 +7980,10 @@
         <v>87</v>
       </c>
       <c r="B387" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="C387" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="D387" s="2"/>
     </row>
@@ -7980,10 +7992,10 @@
         <v>87</v>
       </c>
       <c r="B388" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="C388" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="D388" s="2"/>
     </row>
@@ -7992,7 +8004,7 @@
         <v>87</v>
       </c>
       <c r="B389" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="C389" t="s" s="2">
         <v>211</v>
@@ -8004,13 +8016,13 @@
         <v>87</v>
       </c>
       <c r="B390" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C390" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="D390" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
     </row>
     <row r="391">
@@ -8018,10 +8030,10 @@
         <v>87</v>
       </c>
       <c r="B391" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="C391" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="D391" s="2"/>
     </row>
@@ -8030,10 +8042,10 @@
         <v>87</v>
       </c>
       <c r="B392" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C392" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="D392" s="2"/>
     </row>
@@ -8042,10 +8054,10 @@
         <v>87</v>
       </c>
       <c r="B393" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="C393" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="D393" s="2"/>
     </row>
@@ -8054,10 +8066,10 @@
         <v>87</v>
       </c>
       <c r="B394" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="C394" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="D394" s="2"/>
     </row>
@@ -8066,10 +8078,10 @@
         <v>87</v>
       </c>
       <c r="B395" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="C395" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="D395" s="2"/>
     </row>
@@ -8078,10 +8090,10 @@
         <v>87</v>
       </c>
       <c r="B396" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="C396" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="D396" s="2"/>
     </row>
@@ -8090,10 +8102,10 @@
         <v>87</v>
       </c>
       <c r="B397" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="C397" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="D397" s="2"/>
     </row>
@@ -8102,10 +8114,10 @@
         <v>87</v>
       </c>
       <c r="B398" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C398" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="D398" s="2"/>
     </row>
@@ -8114,10 +8126,10 @@
         <v>87</v>
       </c>
       <c r="B399" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="C399" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="D399" s="2"/>
     </row>
@@ -8126,10 +8138,10 @@
         <v>87</v>
       </c>
       <c r="B400" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="C400" t="s" s="2">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="D400" s="2"/>
     </row>
@@ -8138,10 +8150,10 @@
         <v>87</v>
       </c>
       <c r="B401" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C401" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="D401" s="2"/>
     </row>
@@ -8150,10 +8162,10 @@
         <v>87</v>
       </c>
       <c r="B402" t="s" s="2">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C402" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="D402" s="2"/>
     </row>
@@ -8162,10 +8174,10 @@
         <v>87</v>
       </c>
       <c r="B403" t="s" s="2">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="C403" t="s" s="2">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="D403" s="2"/>
     </row>
@@ -8174,10 +8186,10 @@
         <v>87</v>
       </c>
       <c r="B404" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="C404" t="s" s="2">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="D404" s="2"/>
     </row>
@@ -8186,10 +8198,10 @@
         <v>87</v>
       </c>
       <c r="B405" t="s" s="2">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="C405" t="s" s="2">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="D405" s="2"/>
     </row>
@@ -8198,10 +8210,10 @@
         <v>87</v>
       </c>
       <c r="B406" t="s" s="2">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="C406" t="s" s="2">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="D406" s="2"/>
     </row>
@@ -8210,10 +8222,10 @@
         <v>87</v>
       </c>
       <c r="B407" t="s" s="2">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="C407" t="s" s="2">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="D407" s="2"/>
     </row>
@@ -8222,10 +8234,10 @@
         <v>87</v>
       </c>
       <c r="B408" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="C408" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="D408" s="2"/>
     </row>
@@ -8234,10 +8246,10 @@
         <v>87</v>
       </c>
       <c r="B409" t="s" s="2">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="C409" t="s" s="2">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="D409" s="2"/>
     </row>
@@ -8246,10 +8258,10 @@
         <v>87</v>
       </c>
       <c r="B410" t="s" s="2">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="C410" t="s" s="2">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="D410" s="2"/>
     </row>
@@ -8258,10 +8270,10 @@
         <v>87</v>
       </c>
       <c r="B411" t="s" s="2">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C411" t="s" s="2">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="D411" s="2"/>
     </row>
@@ -8270,10 +8282,10 @@
         <v>87</v>
       </c>
       <c r="B412" t="s" s="2">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="C412" t="s" s="2">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="D412" s="2"/>
     </row>
@@ -8282,10 +8294,10 @@
         <v>87</v>
       </c>
       <c r="B413" t="s" s="2">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="C413" t="s" s="2">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="D413" s="2"/>
     </row>
@@ -8294,10 +8306,10 @@
         <v>87</v>
       </c>
       <c r="B414" t="s" s="2">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="C414" t="s" s="2">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="D414" s="2"/>
     </row>
@@ -8306,10 +8318,10 @@
         <v>87</v>
       </c>
       <c r="B415" t="s" s="2">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="C415" t="s" s="2">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="D415" s="2"/>
     </row>
@@ -8318,10 +8330,10 @@
         <v>87</v>
       </c>
       <c r="B416" t="s" s="2">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="C416" t="s" s="2">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="D416" s="2"/>
     </row>
@@ -8330,13 +8342,13 @@
         <v>87</v>
       </c>
       <c r="B417" t="s" s="2">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="C417" t="s" s="2">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="D417" t="s" s="2">
-        <v>906</v>
+        <v>907</v>
       </c>
     </row>
     <row r="418">
@@ -8344,22 +8356,24 @@
         <v>87</v>
       </c>
       <c r="B418" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="C418" t="s" s="2">
-        <v>908</v>
-      </c>
-      <c r="D418" s="2"/>
+        <v>909</v>
+      </c>
+      <c r="D418" t="s" s="2">
+        <v>910</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="s" s="2">
         <v>87</v>
       </c>
       <c r="B419" t="s" s="2">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="C419" t="s" s="2">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="D419" s="2"/>
     </row>
@@ -8368,10 +8382,10 @@
         <v>87</v>
       </c>
       <c r="B420" t="s" s="2">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="C420" t="s" s="2">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="D420" s="2"/>
     </row>
@@ -8380,10 +8394,10 @@
         <v>87</v>
       </c>
       <c r="B421" t="s" s="2">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="C421" t="s" s="2">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="D421" s="2"/>
     </row>
@@ -8392,10 +8406,10 @@
         <v>87</v>
       </c>
       <c r="B422" t="s" s="2">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="C422" t="s" s="2">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="D422" s="2"/>
     </row>
@@ -8404,10 +8418,10 @@
         <v>87</v>
       </c>
       <c r="B423" t="s" s="2">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="C423" t="s" s="2">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="D423" s="2"/>
     </row>
@@ -8416,27 +8430,25 @@
         <v>87</v>
       </c>
       <c r="B424" t="s" s="2">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="C424" t="s" s="2">
-        <v>920</v>
-      </c>
-      <c r="D424" t="s" s="2">
-        <v>921</v>
-      </c>
+        <v>922</v>
+      </c>
+      <c r="D424" s="2"/>
     </row>
     <row r="425">
       <c r="A425" t="s" s="2">
         <v>87</v>
       </c>
       <c r="B425" t="s" s="2">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="C425" t="s" s="2">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="D425" t="s" s="2">
-        <v>921</v>
+        <v>925</v>
       </c>
     </row>
     <row r="426">
@@ -8444,13 +8456,13 @@
         <v>87</v>
       </c>
       <c r="B426" t="s" s="2">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="C426" t="s" s="2">
+        <v>927</v>
+      </c>
+      <c r="D426" t="s" s="2">
         <v>925</v>
-      </c>
-      <c r="D426" t="s" s="2">
-        <v>921</v>
       </c>
     </row>
     <row r="427">
@@ -8458,25 +8470,39 @@
         <v>87</v>
       </c>
       <c r="B427" t="s" s="2">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="C427" t="s" s="2">
-        <v>927</v>
-      </c>
-      <c r="D427" s="2"/>
+        <v>929</v>
+      </c>
+      <c r="D427" t="s" s="2">
+        <v>925</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="s" s="2">
         <v>87</v>
       </c>
       <c r="B428" t="s" s="2">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="C428" t="s" s="2">
-        <v>929</v>
-      </c>
-      <c r="D428" t="s" s="2">
-        <v>930</v>
+        <v>931</v>
+      </c>
+      <c r="D428" s="2"/>
+    </row>
+    <row r="429">
+      <c r="A429" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="B429" t="s" s="2">
+        <v>932</v>
+      </c>
+      <c r="C429" t="s" s="2">
+        <v>933</v>
+      </c>
+      <c r="D429" t="s" s="2">
+        <v>934</v>
       </c>
     </row>
   </sheetData>
